--- a/research/traditional_assets/database/data/bulgaria/bulgaria_hotel_gaming.xlsx
+++ b/research/traditional_assets/database/data/bulgaria/bulgaria_hotel_gaming.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="bul_alb" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,115 +590,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.0712</v>
+        <v>-0.016</v>
+      </c>
+      <c r="E2">
+        <v>-0.403</v>
       </c>
       <c r="G2">
-        <v>0.1216589861751152</v>
+        <v>0.3024118738404453</v>
       </c>
       <c r="H2">
-        <v>0.1216589861751152</v>
+        <v>0.3024118738404453</v>
       </c>
       <c r="I2">
-        <v>-0.0001612903225806452</v>
+        <v>0.02337662337662338</v>
       </c>
       <c r="J2">
-        <v>-0.0001612903225806452</v>
+        <v>0.01612590799031477</v>
       </c>
       <c r="K2">
-        <v>-2.48</v>
+        <v>0.607</v>
       </c>
       <c r="L2">
-        <v>-0.05714285714285714</v>
+        <v>0.01126159554730983</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.054</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>0.0008780487804878049</v>
       </c>
       <c r="O2">
-        <v>-0</v>
+        <v>0.08896210873146623</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>0.054</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>0.0008780487804878049</v>
       </c>
       <c r="R2">
-        <v>-0</v>
+        <v>0.08896210873146623</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
+      <c r="T2">
+        <v>0</v>
+      </c>
       <c r="U2">
-        <v>9.970000000000001</v>
+        <v>3.38</v>
       </c>
       <c r="V2">
-        <v>0.1311842105263158</v>
+        <v>0.05495934959349593</v>
       </c>
       <c r="W2">
-        <v>-0.00862009037191519</v>
+        <v>0.002174068767908309</v>
       </c>
       <c r="X2">
-        <v>0.1019441901236031</v>
+        <v>0.1521799214214302</v>
       </c>
       <c r="Y2">
-        <v>-0.1105642804955183</v>
+        <v>-0.1500058526535219</v>
       </c>
       <c r="Z2">
-        <v>0.1312883806758024</v>
+        <v>0.1647310513447433</v>
       </c>
       <c r="AA2">
-        <v>-2.117554527029071e-05</v>
+        <v>0.002656437777133148</v>
       </c>
       <c r="AB2">
-        <v>0.07346724323951552</v>
+        <v>0.1105144208306309</v>
       </c>
       <c r="AC2">
-        <v>-0.07348841878478581</v>
+        <v>-0.1078579830534978</v>
       </c>
       <c r="AD2">
-        <v>53.8</v>
+        <v>50.9</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>53.8</v>
+        <v>50.9</v>
       </c>
       <c r="AG2">
-        <v>43.83</v>
+        <v>47.52</v>
       </c>
       <c r="AH2">
-        <v>0.4144838212634822</v>
+        <v>0.4528469750889679</v>
       </c>
       <c r="AI2">
-        <v>0.1565774155995343</v>
+        <v>0.1585175957645593</v>
       </c>
       <c r="AJ2">
-        <v>0.3657681715763999</v>
+        <v>0.4358833241607044</v>
       </c>
       <c r="AK2">
-        <v>0.131373077960615</v>
+        <v>0.1495656552939695</v>
       </c>
       <c r="AL2">
-        <v>1.75</v>
+        <v>0.79</v>
       </c>
       <c r="AM2">
-        <v>1.729</v>
+        <v>0.762</v>
       </c>
       <c r="AN2">
-        <v>4.045112781954887</v>
+        <v>4.241666666666666</v>
       </c>
       <c r="AO2">
-        <v>-0.004</v>
+        <v>1.594936708860759</v>
       </c>
       <c r="AP2">
-        <v>3.295488721804511</v>
+        <v>3.96</v>
       </c>
       <c r="AQ2">
-        <v>-0.004048582995951417</v>
+        <v>1.653543307086614</v>
       </c>
     </row>
     <row r="3">
@@ -716,115 +724,8833 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.0712</v>
+        <v>-0.016</v>
+      </c>
+      <c r="E3">
+        <v>-0.403</v>
       </c>
       <c r="G3">
-        <v>0.1216589861751152</v>
+        <v>0.3024118738404453</v>
       </c>
       <c r="H3">
-        <v>0.1216589861751152</v>
+        <v>0.3024118738404453</v>
       </c>
       <c r="I3">
-        <v>-0.0001612903225806452</v>
+        <v>0.02337662337662338</v>
       </c>
       <c r="J3">
-        <v>-0.0001612903225806452</v>
+        <v>0.01612590799031477</v>
       </c>
       <c r="K3">
-        <v>-2.48</v>
+        <v>0.607</v>
       </c>
       <c r="L3">
-        <v>-0.05714285714285714</v>
+        <v>0.01126159554730983</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>0.054</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.0008780487804878049</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>0.08896210873146623</v>
       </c>
       <c r="P3">
-        <v>-0</v>
+        <v>0.054</v>
       </c>
       <c r="Q3">
-        <v>-0</v>
+        <v>0.0008780487804878049</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>0.08896210873146623</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
       <c r="U3">
-        <v>9.970000000000001</v>
+        <v>3.38</v>
       </c>
       <c r="V3">
-        <v>0.1311842105263158</v>
+        <v>0.05495934959349593</v>
       </c>
       <c r="W3">
-        <v>-0.00862009037191519</v>
+        <v>0.002174068767908309</v>
       </c>
       <c r="X3">
-        <v>0.1019441901236031</v>
+        <v>0.1521799214214302</v>
       </c>
       <c r="Y3">
-        <v>-0.1105642804955183</v>
+        <v>-0.1500058526535219</v>
       </c>
       <c r="Z3">
-        <v>0.1312883806758024</v>
+        <v>0.1647310513447433</v>
       </c>
       <c r="AA3">
-        <v>-2.117554527029071e-05</v>
+        <v>0.002656437777133148</v>
       </c>
       <c r="AB3">
-        <v>0.07346724323951552</v>
+        <v>0.1105144208306309</v>
       </c>
       <c r="AC3">
-        <v>-0.07348841878478581</v>
+        <v>-0.1078579830534978</v>
       </c>
       <c r="AD3">
-        <v>53.8</v>
+        <v>50.9</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>53.8</v>
+        <v>50.9</v>
       </c>
       <c r="AG3">
-        <v>43.83</v>
+        <v>47.52</v>
       </c>
       <c r="AH3">
-        <v>0.4144838212634822</v>
+        <v>0.4528469750889679</v>
       </c>
       <c r="AI3">
-        <v>0.1565774155995343</v>
+        <v>0.1585175957645593</v>
       </c>
       <c r="AJ3">
-        <v>0.3657681715763999</v>
+        <v>0.4358833241607044</v>
       </c>
       <c r="AK3">
-        <v>0.131373077960615</v>
+        <v>0.1495656552939695</v>
       </c>
       <c r="AL3">
-        <v>1.75</v>
+        <v>0.79</v>
       </c>
       <c r="AM3">
-        <v>1.729</v>
+        <v>0.762</v>
       </c>
       <c r="AN3">
-        <v>4.045112781954887</v>
+        <v>4.241666666666666</v>
       </c>
       <c r="AO3">
-        <v>-0.004</v>
+        <v>1.594936708860759</v>
       </c>
       <c r="AP3">
-        <v>3.295488721804511</v>
+        <v>3.96</v>
       </c>
       <c r="AQ3">
-        <v>-0.004048582995951417</v>
+        <v>1.653543307086614</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AQ2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_capital</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>actual_equity_value</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>actual_enterprise_value</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_capital</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_rating</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>actual_beta</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Albena AD (BUL:ALB)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>BUL:ALB</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Hotel/Gaming</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>0.452846975088968</v>
+      </c>
+      <c r="F2">
+        <v>0.17</v>
+      </c>
+      <c r="G2">
+        <v>61.5</v>
+      </c>
+      <c r="H2">
+        <v>105.919510035088</v>
+      </c>
+      <c r="I2">
+        <v>109.02</v>
+      </c>
+      <c r="J2">
+        <v>121.647510035088</v>
+      </c>
+      <c r="K2">
+        <v>50.9</v>
+      </c>
+      <c r="L2">
+        <v>19.108</v>
+      </c>
+      <c r="M2">
+        <v>0.110514420830631</v>
+      </c>
+      <c r="N2">
+        <v>0.103070170073356</v>
+      </c>
+      <c r="O2">
+        <v>0.0601720183486239</v>
+      </c>
+      <c r="P2">
+        <v>0.04113</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="S2">
+        <v>0.15217992142143</v>
+      </c>
+      <c r="T2">
+        <v>0.115756710931754</v>
+      </c>
+      <c r="U2">
+        <v>1.30725775089335</v>
+      </c>
+      <c r="V2">
+        <v>0.887302227656864</v>
+      </c>
+      <c r="W2">
+        <v>12.95870209597501</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0.0388</v>
+      </c>
+      <c r="AA2">
+        <v>61.5</v>
+      </c>
+      <c r="AB2">
+        <v>0.08673111430699013</v>
+      </c>
+      <c r="AC2">
+        <v>0.06685779816513762</v>
+      </c>
+      <c r="AD2">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="AF2">
+        <v>1</v>
+      </c>
+      <c r="AG2">
+        <v>12</v>
+      </c>
+      <c r="AH2">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="AI2">
+        <v>10.1</v>
+      </c>
+      <c r="AJ2">
+        <v>50.9</v>
+      </c>
+      <c r="AK2">
+        <v>50.9</v>
+      </c>
+      <c r="AL2">
+        <v>0.79</v>
+      </c>
+      <c r="AM2">
+        <v>50.9</v>
+      </c>
+      <c r="AN2">
+        <v>3.38</v>
+      </c>
+      <c r="AO2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ2">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.1037787081112474</v>
+      </c>
+      <c r="C2">
+        <v>123.7010464814102</v>
+      </c>
+      <c r="D2">
+        <v>120.3210464814102</v>
+      </c>
+      <c r="E2">
+        <v>-50.9</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>3.38</v>
+      </c>
+      <c r="H2">
+        <v>61.5</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>12</v>
+      </c>
+      <c r="K2">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="L2">
+        <v>11.316</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>11.316</v>
+      </c>
+      <c r="O2">
+        <v>1.1316</v>
+      </c>
+      <c r="P2">
+        <v>10.1844</v>
+      </c>
+      <c r="Q2">
+        <v>10.8684</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.1037787081112474</v>
+      </c>
+      <c r="T2">
+        <v>0.7491972013786339</v>
+      </c>
+      <c r="U2">
+        <v>0.0457</v>
+      </c>
+      <c r="V2">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W2">
+        <v>0.04113000000000001</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.1037370294031361</v>
+      </c>
+      <c r="C3">
+        <v>122.6542724620568</v>
+      </c>
+      <c r="D3">
+        <v>120.3982724620568</v>
+      </c>
+      <c r="E3">
+        <v>-49.776</v>
+      </c>
+      <c r="F3">
+        <v>1.124</v>
+      </c>
+      <c r="G3">
+        <v>3.38</v>
+      </c>
+      <c r="H3">
+        <v>61.5</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>12</v>
+      </c>
+      <c r="K3">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="L3">
+        <v>11.316</v>
+      </c>
+      <c r="M3">
+        <v>0.05136680000000001</v>
+      </c>
+      <c r="N3">
+        <v>11.2646332</v>
+      </c>
+      <c r="O3">
+        <v>1.12646332</v>
+      </c>
+      <c r="P3">
+        <v>10.13816988</v>
+      </c>
+      <c r="Q3">
+        <v>10.82216988</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.1043694236395315</v>
+      </c>
+      <c r="T3">
+        <v>0.7560080850275305</v>
+      </c>
+      <c r="U3">
+        <v>0.0457</v>
+      </c>
+      <c r="V3">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W3">
+        <v>0.04113000000000001</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>220.2979356315752</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.1036953506950249</v>
+      </c>
+      <c r="C4">
+        <v>121.6075976386881</v>
+      </c>
+      <c r="D4">
+        <v>120.4755976386881</v>
+      </c>
+      <c r="E4">
+        <v>-48.652</v>
+      </c>
+      <c r="F4">
+        <v>2.248</v>
+      </c>
+      <c r="G4">
+        <v>3.38</v>
+      </c>
+      <c r="H4">
+        <v>61.5</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>12</v>
+      </c>
+      <c r="K4">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="L4">
+        <v>11.316</v>
+      </c>
+      <c r="M4">
+        <v>0.1027336</v>
+      </c>
+      <c r="N4">
+        <v>11.2132664</v>
+      </c>
+      <c r="O4">
+        <v>1.12132664</v>
+      </c>
+      <c r="P4">
+        <v>10.09193976</v>
+      </c>
+      <c r="Q4">
+        <v>10.77593976</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.1049721945867601</v>
+      </c>
+      <c r="T4">
+        <v>0.7629579663019149</v>
+      </c>
+      <c r="U4">
+        <v>0.0457</v>
+      </c>
+      <c r="V4">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W4">
+        <v>0.04113000000000001</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>110.1489678157876</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.1036536719869136</v>
+      </c>
+      <c r="C5">
+        <v>120.5610222025513</v>
+      </c>
+      <c r="D5">
+        <v>120.5530222025513</v>
+      </c>
+      <c r="E5">
+        <v>-47.528</v>
+      </c>
+      <c r="F5">
+        <v>3.372</v>
+      </c>
+      <c r="G5">
+        <v>3.38</v>
+      </c>
+      <c r="H5">
+        <v>61.5</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>12</v>
+      </c>
+      <c r="K5">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="L5">
+        <v>11.316</v>
+      </c>
+      <c r="M5">
+        <v>0.1541004</v>
+      </c>
+      <c r="N5">
+        <v>11.1618996</v>
+      </c>
+      <c r="O5">
+        <v>1.11618996</v>
+      </c>
+      <c r="P5">
+        <v>10.04570964</v>
+      </c>
+      <c r="Q5">
+        <v>10.72970964</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.1055873938009419</v>
+      </c>
+      <c r="T5">
+        <v>0.7700511440974205</v>
+      </c>
+      <c r="U5">
+        <v>0.0457</v>
+      </c>
+      <c r="V5">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W5">
+        <v>0.04113000000000001</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>73.43264521052508</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.1036119932788024</v>
+      </c>
+      <c r="C6">
+        <v>119.5145463453854</v>
+      </c>
+      <c r="D6">
+        <v>120.6305463453854</v>
+      </c>
+      <c r="E6">
+        <v>-46.404</v>
+      </c>
+      <c r="F6">
+        <v>4.496</v>
+      </c>
+      <c r="G6">
+        <v>3.38</v>
+      </c>
+      <c r="H6">
+        <v>61.5</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>12</v>
+      </c>
+      <c r="K6">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="L6">
+        <v>11.316</v>
+      </c>
+      <c r="M6">
+        <v>0.2054672</v>
+      </c>
+      <c r="N6">
+        <v>11.1105328</v>
+      </c>
+      <c r="O6">
+        <v>1.11105328</v>
+      </c>
+      <c r="P6">
+        <v>9.999479520000001</v>
+      </c>
+      <c r="Q6">
+        <v>10.68347952</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.1062154096654192</v>
+      </c>
+      <c r="T6">
+        <v>0.7772920964303327</v>
+      </c>
+      <c r="U6">
+        <v>0.0457</v>
+      </c>
+      <c r="V6">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W6">
+        <v>0.04113000000000001</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>55.07448390789381</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.1035703145706912</v>
+      </c>
+      <c r="C7">
+        <v>118.4681702594231</v>
+      </c>
+      <c r="D7">
+        <v>120.7081702594231</v>
+      </c>
+      <c r="E7">
+        <v>-45.28</v>
+      </c>
+      <c r="F7">
+        <v>5.620000000000001</v>
+      </c>
+      <c r="G7">
+        <v>3.38</v>
+      </c>
+      <c r="H7">
+        <v>61.5</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>12</v>
+      </c>
+      <c r="K7">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="L7">
+        <v>11.316</v>
+      </c>
+      <c r="M7">
+        <v>0.2568340000000001</v>
+      </c>
+      <c r="N7">
+        <v>11.059166</v>
+      </c>
+      <c r="O7">
+        <v>1.1059166</v>
+      </c>
+      <c r="P7">
+        <v>9.953249400000001</v>
+      </c>
+      <c r="Q7">
+        <v>10.6372494</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.106856646916517</v>
+      </c>
+      <c r="T7">
+        <v>0.7846854898649902</v>
+      </c>
+      <c r="U7">
+        <v>0.0457</v>
+      </c>
+      <c r="V7">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W7">
+        <v>0.04113000000000001</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>44.05958712631504</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.1035286358625799</v>
+      </c>
+      <c r="C8">
+        <v>117.4218941373921</v>
+      </c>
+      <c r="D8">
+        <v>120.7858941373921</v>
+      </c>
+      <c r="E8">
+        <v>-44.156</v>
+      </c>
+      <c r="F8">
+        <v>6.744</v>
+      </c>
+      <c r="G8">
+        <v>3.38</v>
+      </c>
+      <c r="H8">
+        <v>61.5</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>12</v>
+      </c>
+      <c r="K8">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="L8">
+        <v>11.316</v>
+      </c>
+      <c r="M8">
+        <v>0.3082008</v>
+      </c>
+      <c r="N8">
+        <v>11.0077992</v>
+      </c>
+      <c r="O8">
+        <v>1.10077992</v>
+      </c>
+      <c r="P8">
+        <v>9.90701928</v>
+      </c>
+      <c r="Q8">
+        <v>10.59101928</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.1075115275133829</v>
+      </c>
+      <c r="T8">
+        <v>0.7922361895429384</v>
+      </c>
+      <c r="U8">
+        <v>0.0457</v>
+      </c>
+      <c r="V8">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W8">
+        <v>0.04113000000000001</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>36.71632260526255</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.1034869571544687</v>
+      </c>
+      <c r="C9">
+        <v>116.375718172517</v>
+      </c>
+      <c r="D9">
+        <v>120.863718172517</v>
+      </c>
+      <c r="E9">
+        <v>-43.032</v>
+      </c>
+      <c r="F9">
+        <v>7.868000000000001</v>
+      </c>
+      <c r="G9">
+        <v>3.38</v>
+      </c>
+      <c r="H9">
+        <v>61.5</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>12</v>
+      </c>
+      <c r="K9">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="L9">
+        <v>11.316</v>
+      </c>
+      <c r="M9">
+        <v>0.3595676000000001</v>
+      </c>
+      <c r="N9">
+        <v>10.9564324</v>
+      </c>
+      <c r="O9">
+        <v>1.09564324</v>
+      </c>
+      <c r="P9">
+        <v>9.860789160000001</v>
+      </c>
+      <c r="Q9">
+        <v>10.54478916</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.1081804915639448</v>
+      </c>
+      <c r="T9">
+        <v>0.7999492698591221</v>
+      </c>
+      <c r="U9">
+        <v>0.0457</v>
+      </c>
+      <c r="V9">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W9">
+        <v>0.04113000000000001</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>31.4711336616536</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.1034452784463574</v>
+      </c>
+      <c r="C10">
+        <v>115.3296425585204</v>
+      </c>
+      <c r="D10">
+        <v>120.9416425585204</v>
+      </c>
+      <c r="E10">
+        <v>-41.908</v>
+      </c>
+      <c r="F10">
+        <v>8.992000000000001</v>
+      </c>
+      <c r="G10">
+        <v>3.38</v>
+      </c>
+      <c r="H10">
+        <v>61.5</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>12</v>
+      </c>
+      <c r="K10">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="L10">
+        <v>11.316</v>
+      </c>
+      <c r="M10">
+        <v>0.4109344000000001</v>
+      </c>
+      <c r="N10">
+        <v>10.9050656</v>
+      </c>
+      <c r="O10">
+        <v>1.09050656</v>
+      </c>
+      <c r="P10">
+        <v>9.814559040000001</v>
+      </c>
+      <c r="Q10">
+        <v>10.49855904</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.1088639983112581</v>
+      </c>
+      <c r="T10">
+        <v>0.807830025834353</v>
+      </c>
+      <c r="U10">
+        <v>0.0457</v>
+      </c>
+      <c r="V10">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W10">
+        <v>0.04113000000000001</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>27.5372419539469</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.1034035997382462</v>
+      </c>
+      <c r="C11">
+        <v>114.2836674896251</v>
+      </c>
+      <c r="D11">
+        <v>121.0196674896251</v>
+      </c>
+      <c r="E11">
+        <v>-40.784</v>
+      </c>
+      <c r="F11">
+        <v>10.116</v>
+      </c>
+      <c r="G11">
+        <v>3.38</v>
+      </c>
+      <c r="H11">
+        <v>61.5</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>12</v>
+      </c>
+      <c r="K11">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="L11">
+        <v>11.316</v>
+      </c>
+      <c r="M11">
+        <v>0.4623012</v>
+      </c>
+      <c r="N11">
+        <v>10.8536988</v>
+      </c>
+      <c r="O11">
+        <v>1.08536988</v>
+      </c>
+      <c r="P11">
+        <v>9.76832892</v>
+      </c>
+      <c r="Q11">
+        <v>10.45232892</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.1095625271848859</v>
+      </c>
+      <c r="T11">
+        <v>0.8158839852376111</v>
+      </c>
+      <c r="U11">
+        <v>0.0457</v>
+      </c>
+      <c r="V11">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W11">
+        <v>0.04113000000000001</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>24.47754840350836</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.1033619210301349</v>
+      </c>
+      <c r="C12">
+        <v>113.2377931605552</v>
+      </c>
+      <c r="D12">
+        <v>121.0977931605552</v>
+      </c>
+      <c r="E12">
+        <v>-39.66</v>
+      </c>
+      <c r="F12">
+        <v>11.24</v>
+      </c>
+      <c r="G12">
+        <v>3.38</v>
+      </c>
+      <c r="H12">
+        <v>61.5</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>12</v>
+      </c>
+      <c r="K12">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="L12">
+        <v>11.316</v>
+      </c>
+      <c r="M12">
+        <v>0.5136680000000001</v>
+      </c>
+      <c r="N12">
+        <v>10.802332</v>
+      </c>
+      <c r="O12">
+        <v>1.0802332</v>
+      </c>
+      <c r="P12">
+        <v>9.722098799999999</v>
+      </c>
+      <c r="Q12">
+        <v>10.4060988</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.1102765789223721</v>
+      </c>
+      <c r="T12">
+        <v>0.8241169215164973</v>
+      </c>
+      <c r="U12">
+        <v>0.0457</v>
+      </c>
+      <c r="V12">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W12">
+        <v>0.04113000000000001</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>22.02979356315752</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.1033202423220237</v>
+      </c>
+      <c r="C13">
+        <v>112.1920197665383</v>
+      </c>
+      <c r="D13">
+        <v>121.1760197665383</v>
+      </c>
+      <c r="E13">
+        <v>-38.536</v>
+      </c>
+      <c r="F13">
+        <v>12.364</v>
+      </c>
+      <c r="G13">
+        <v>3.38</v>
+      </c>
+      <c r="H13">
+        <v>61.5</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>12</v>
+      </c>
+      <c r="K13">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="L13">
+        <v>11.316</v>
+      </c>
+      <c r="M13">
+        <v>0.5650348000000001</v>
+      </c>
+      <c r="N13">
+        <v>10.7509652</v>
+      </c>
+      <c r="O13">
+        <v>1.07509652</v>
+      </c>
+      <c r="P13">
+        <v>9.675868680000001</v>
+      </c>
+      <c r="Q13">
+        <v>10.35986868</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.1110066767663187</v>
+      </c>
+      <c r="T13">
+        <v>0.8325348675994032</v>
+      </c>
+      <c r="U13">
+        <v>0.0457</v>
+      </c>
+      <c r="V13">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W13">
+        <v>0.04113000000000001</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>20.02708505741593</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.1032785636139124</v>
+      </c>
+      <c r="C14">
+        <v>111.1463475033063</v>
+      </c>
+      <c r="D14">
+        <v>121.2543475033063</v>
+      </c>
+      <c r="E14">
+        <v>-37.412</v>
+      </c>
+      <c r="F14">
+        <v>13.488</v>
+      </c>
+      <c r="G14">
+        <v>3.38</v>
+      </c>
+      <c r="H14">
+        <v>61.5</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>12</v>
+      </c>
+      <c r="K14">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="L14">
+        <v>11.316</v>
+      </c>
+      <c r="M14">
+        <v>0.6164016</v>
+      </c>
+      <c r="N14">
+        <v>10.6995984</v>
+      </c>
+      <c r="O14">
+        <v>1.06995984</v>
+      </c>
+      <c r="P14">
+        <v>9.629638560000002</v>
+      </c>
+      <c r="Q14">
+        <v>10.31363856</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.1117533677430823</v>
+      </c>
+      <c r="T14">
+        <v>0.8411441306387391</v>
+      </c>
+      <c r="U14">
+        <v>0.0457</v>
+      </c>
+      <c r="V14">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W14">
+        <v>0.04113000000000001</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>18.35816130263127</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.1032368849058012</v>
+      </c>
+      <c r="C15">
+        <v>110.1007765670979</v>
+      </c>
+      <c r="D15">
+        <v>121.332776567098</v>
+      </c>
+      <c r="E15">
+        <v>-36.288</v>
+      </c>
+      <c r="F15">
+        <v>14.612</v>
+      </c>
+      <c r="G15">
+        <v>3.38</v>
+      </c>
+      <c r="H15">
+        <v>61.5</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>12</v>
+      </c>
+      <c r="K15">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="L15">
+        <v>11.316</v>
+      </c>
+      <c r="M15">
+        <v>0.6677684000000002</v>
+      </c>
+      <c r="N15">
+        <v>10.6482316</v>
+      </c>
+      <c r="O15">
+        <v>1.06482316</v>
+      </c>
+      <c r="P15">
+        <v>9.583408440000001</v>
+      </c>
+      <c r="Q15">
+        <v>10.26740844</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.1125172240296565</v>
+      </c>
+      <c r="T15">
+        <v>0.8499513077709329</v>
+      </c>
+      <c r="U15">
+        <v>0.0457</v>
+      </c>
+      <c r="V15">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W15">
+        <v>0.04113000000000001</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>16.94599504858271</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.1031952061976899</v>
+      </c>
+      <c r="C16">
+        <v>109.0553071546597</v>
+      </c>
+      <c r="D16">
+        <v>121.4113071546598</v>
+      </c>
+      <c r="E16">
+        <v>-35.16399999999999</v>
+      </c>
+      <c r="F16">
+        <v>15.736</v>
+      </c>
+      <c r="G16">
+        <v>3.38</v>
+      </c>
+      <c r="H16">
+        <v>61.5</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>12</v>
+      </c>
+      <c r="K16">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="L16">
+        <v>11.316</v>
+      </c>
+      <c r="M16">
+        <v>0.7191352000000002</v>
+      </c>
+      <c r="N16">
+        <v>10.5968648</v>
+      </c>
+      <c r="O16">
+        <v>1.05968648</v>
+      </c>
+      <c r="P16">
+        <v>9.537178320000001</v>
+      </c>
+      <c r="Q16">
+        <v>10.22117832</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.1132988444159185</v>
+      </c>
+      <c r="T16">
+        <v>0.8589633029759686</v>
+      </c>
+      <c r="U16">
+        <v>0.0457</v>
+      </c>
+      <c r="V16">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W16">
+        <v>0.04113000000000001</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>15.7355668308268</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.1031535274895787</v>
+      </c>
+      <c r="C17">
+        <v>108.009939463248</v>
+      </c>
+      <c r="D17">
+        <v>121.489939463248</v>
+      </c>
+      <c r="E17">
+        <v>-34.04</v>
+      </c>
+      <c r="F17">
+        <v>16.86</v>
+      </c>
+      <c r="G17">
+        <v>3.38</v>
+      </c>
+      <c r="H17">
+        <v>61.5</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>12</v>
+      </c>
+      <c r="K17">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="L17">
+        <v>11.316</v>
+      </c>
+      <c r="M17">
+        <v>0.770502</v>
+      </c>
+      <c r="N17">
+        <v>10.545498</v>
+      </c>
+      <c r="O17">
+        <v>1.0545498</v>
+      </c>
+      <c r="P17">
+        <v>9.4909482</v>
+      </c>
+      <c r="Q17">
+        <v>10.1749482</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.1140988558700926</v>
+      </c>
+      <c r="T17">
+        <v>0.8681873451270052</v>
+      </c>
+      <c r="U17">
+        <v>0.0457</v>
+      </c>
+      <c r="V17">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W17">
+        <v>0.04113000000000001</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>14.68652904210502</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.1031118487814674</v>
+      </c>
+      <c r="C18">
+        <v>106.9646736906304</v>
+      </c>
+      <c r="D18">
+        <v>121.5686736906304</v>
+      </c>
+      <c r="E18">
+        <v>-32.916</v>
+      </c>
+      <c r="F18">
+        <v>17.984</v>
+      </c>
+      <c r="G18">
+        <v>3.38</v>
+      </c>
+      <c r="H18">
+        <v>61.5</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>12</v>
+      </c>
+      <c r="K18">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="L18">
+        <v>11.316</v>
+      </c>
+      <c r="M18">
+        <v>0.8218688000000002</v>
+      </c>
+      <c r="N18">
+        <v>10.4941312</v>
+      </c>
+      <c r="O18">
+        <v>1.04941312</v>
+      </c>
+      <c r="P18">
+        <v>9.444718079999999</v>
+      </c>
+      <c r="Q18">
+        <v>10.12871808</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.1149179152160327</v>
+      </c>
+      <c r="T18">
+        <v>0.8776310073292569</v>
+      </c>
+      <c r="U18">
+        <v>0.0457</v>
+      </c>
+      <c r="V18">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W18">
+        <v>0.04113000000000001</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>13.76862097697345</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.1030701700733562</v>
+      </c>
+      <c r="C19">
+        <v>105.9195100350876</v>
+      </c>
+      <c r="D19">
+        <v>121.6475100350876</v>
+      </c>
+      <c r="E19">
+        <v>-31.79199999999999</v>
+      </c>
+      <c r="F19">
+        <v>19.108</v>
+      </c>
+      <c r="G19">
+        <v>3.38</v>
+      </c>
+      <c r="H19">
+        <v>61.5</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>12</v>
+      </c>
+      <c r="K19">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="L19">
+        <v>11.316</v>
+      </c>
+      <c r="M19">
+        <v>0.8732356000000002</v>
+      </c>
+      <c r="N19">
+        <v>10.4427644</v>
+      </c>
+      <c r="O19">
+        <v>1.04427644</v>
+      </c>
+      <c r="P19">
+        <v>9.398487960000001</v>
+      </c>
+      <c r="Q19">
+        <v>10.08248796</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.1157567109317545</v>
+      </c>
+      <c r="T19">
+        <v>0.887302227656864</v>
+      </c>
+      <c r="U19">
+        <v>0.0457</v>
+      </c>
+      <c r="V19">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W19">
+        <v>0.04113000000000001</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>12.95870209597501</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.103287691365245</v>
+      </c>
+      <c r="C20">
+        <v>104.3851848555426</v>
+      </c>
+      <c r="D20">
+        <v>121.2371848555426</v>
+      </c>
+      <c r="E20">
+        <v>-30.668</v>
+      </c>
+      <c r="F20">
+        <v>20.232</v>
+      </c>
+      <c r="G20">
+        <v>3.38</v>
+      </c>
+      <c r="H20">
+        <v>61.5</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>12</v>
+      </c>
+      <c r="K20">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="L20">
+        <v>11.316</v>
+      </c>
+      <c r="M20">
+        <v>0.9569736</v>
+      </c>
+      <c r="N20">
+        <v>10.3590264</v>
+      </c>
+      <c r="O20">
+        <v>1.03590264</v>
+      </c>
+      <c r="P20">
+        <v>9.323123760000001</v>
+      </c>
+      <c r="Q20">
+        <v>10.00712376</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.116615965079567</v>
+      </c>
+      <c r="T20">
+        <v>0.8972093314070957</v>
+      </c>
+      <c r="U20">
+        <v>0.0473</v>
+      </c>
+      <c r="V20">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W20">
+        <v>0.04257</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>11.82477761142</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.1032604126571337</v>
+      </c>
+      <c r="C21">
+        <v>103.3124906669946</v>
+      </c>
+      <c r="D21">
+        <v>121.2884906669946</v>
+      </c>
+      <c r="E21">
+        <v>-29.544</v>
+      </c>
+      <c r="F21">
+        <v>21.356</v>
+      </c>
+      <c r="G21">
+        <v>3.38</v>
+      </c>
+      <c r="H21">
+        <v>61.5</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>12</v>
+      </c>
+      <c r="K21">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="L21">
+        <v>11.316</v>
+      </c>
+      <c r="M21">
+        <v>1.0101388</v>
+      </c>
+      <c r="N21">
+        <v>10.3058612</v>
+      </c>
+      <c r="O21">
+        <v>1.03058612</v>
+      </c>
+      <c r="P21">
+        <v>9.27527508</v>
+      </c>
+      <c r="Q21">
+        <v>9.959275079999999</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.1174964353791774</v>
+      </c>
+      <c r="T21">
+        <v>0.9073610550030121</v>
+      </c>
+      <c r="U21">
+        <v>0.0473</v>
+      </c>
+      <c r="V21">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W21">
+        <v>0.04257</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>11.20242089502947</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.1032331339490224</v>
+      </c>
+      <c r="C22">
+        <v>102.2398399205755</v>
+      </c>
+      <c r="D22">
+        <v>121.3398399205755</v>
+      </c>
+      <c r="E22">
+        <v>-28.41999999999999</v>
+      </c>
+      <c r="F22">
+        <v>22.48</v>
+      </c>
+      <c r="G22">
+        <v>3.38</v>
+      </c>
+      <c r="H22">
+        <v>61.5</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>12</v>
+      </c>
+      <c r="K22">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="L22">
+        <v>11.316</v>
+      </c>
+      <c r="M22">
+        <v>1.063304</v>
+      </c>
+      <c r="N22">
+        <v>10.252696</v>
+      </c>
+      <c r="O22">
+        <v>1.0252696</v>
+      </c>
+      <c r="P22">
+        <v>9.227426400000001</v>
+      </c>
+      <c r="Q22">
+        <v>9.9114264</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.1183989174362781</v>
+      </c>
+      <c r="T22">
+        <v>0.9177665716888266</v>
+      </c>
+      <c r="U22">
+        <v>0.0473</v>
+      </c>
+      <c r="V22">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W22">
+        <v>0.04257</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>10.642299850278</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.1039240552409112</v>
+      </c>
+      <c r="C23">
+        <v>99.82850794093497</v>
+      </c>
+      <c r="D23">
+        <v>120.052507940935</v>
+      </c>
+      <c r="E23">
+        <v>-27.296</v>
+      </c>
+      <c r="F23">
+        <v>23.604</v>
+      </c>
+      <c r="G23">
+        <v>3.38</v>
+      </c>
+      <c r="H23">
+        <v>61.5</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>12</v>
+      </c>
+      <c r="K23">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="L23">
+        <v>11.316</v>
+      </c>
+      <c r="M23">
+        <v>1.2061644</v>
+      </c>
+      <c r="N23">
+        <v>10.1098356</v>
+      </c>
+      <c r="O23">
+        <v>1.01098356</v>
+      </c>
+      <c r="P23">
+        <v>9.098852040000001</v>
+      </c>
+      <c r="Q23">
+        <v>9.78285204</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.1193242471403939</v>
+      </c>
+      <c r="T23">
+        <v>0.9284355191768133</v>
+      </c>
+      <c r="U23">
+        <v>0.0511</v>
+      </c>
+      <c r="V23">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W23">
+        <v>0.04599</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>9.381805664302478</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.1039309765328</v>
+      </c>
+      <c r="C24">
+        <v>98.69175028714767</v>
+      </c>
+      <c r="D24">
+        <v>120.0397502871477</v>
+      </c>
+      <c r="E24">
+        <v>-26.172</v>
+      </c>
+      <c r="F24">
+        <v>24.728</v>
+      </c>
+      <c r="G24">
+        <v>3.38</v>
+      </c>
+      <c r="H24">
+        <v>61.5</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>12</v>
+      </c>
+      <c r="K24">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="L24">
+        <v>11.316</v>
+      </c>
+      <c r="M24">
+        <v>1.2636008</v>
+      </c>
+      <c r="N24">
+        <v>10.0523992</v>
+      </c>
+      <c r="O24">
+        <v>1.00523992</v>
+      </c>
+      <c r="P24">
+        <v>9.047159280000001</v>
+      </c>
+      <c r="Q24">
+        <v>9.73115928</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.1202733032471794</v>
+      </c>
+      <c r="T24">
+        <v>0.9393780294209024</v>
+      </c>
+      <c r="U24">
+        <v>0.0511</v>
+      </c>
+      <c r="V24">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W24">
+        <v>0.04599</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>8.955359952288727</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.1039378978246887</v>
+      </c>
+      <c r="C25">
+        <v>97.55499534451464</v>
+      </c>
+      <c r="D25">
+        <v>120.0269953445146</v>
+      </c>
+      <c r="E25">
+        <v>-25.04799999999999</v>
+      </c>
+      <c r="F25">
+        <v>25.852</v>
+      </c>
+      <c r="G25">
+        <v>3.38</v>
+      </c>
+      <c r="H25">
+        <v>61.5</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>12</v>
+      </c>
+      <c r="K25">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="L25">
+        <v>11.316</v>
+      </c>
+      <c r="M25">
+        <v>1.3210372</v>
+      </c>
+      <c r="N25">
+        <v>9.9949628</v>
+      </c>
+      <c r="O25">
+        <v>0.9994962799999998</v>
+      </c>
+      <c r="P25">
+        <v>8.995466520000001</v>
+      </c>
+      <c r="Q25">
+        <v>9.67946652</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.1212470101619334</v>
+      </c>
+      <c r="T25">
+        <v>0.9506047607102927</v>
+      </c>
+      <c r="U25">
+        <v>0.0511</v>
+      </c>
+      <c r="V25">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W25">
+        <v>0.04599</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>8.565996476102262</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.1039448191165774</v>
+      </c>
+      <c r="C26">
+        <v>96.41824311217177</v>
+      </c>
+      <c r="D26">
+        <v>120.0142431121718</v>
+      </c>
+      <c r="E26">
+        <v>-23.924</v>
+      </c>
+      <c r="F26">
+        <v>26.976</v>
+      </c>
+      <c r="G26">
+        <v>3.38</v>
+      </c>
+      <c r="H26">
+        <v>61.5</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>12</v>
+      </c>
+      <c r="K26">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="L26">
+        <v>11.316</v>
+      </c>
+      <c r="M26">
+        <v>1.3784736</v>
+      </c>
+      <c r="N26">
+        <v>9.937526400000001</v>
+      </c>
+      <c r="O26">
+        <v>0.9937526399999999</v>
+      </c>
+      <c r="P26">
+        <v>8.943773760000001</v>
+      </c>
+      <c r="Q26">
+        <v>9.62777376</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.1222463409428651</v>
+      </c>
+      <c r="T26">
+        <v>0.9621269322967719</v>
+      </c>
+      <c r="U26">
+        <v>0.0511</v>
+      </c>
+      <c r="V26">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W26">
+        <v>0.04599</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>8.20907995626467</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.1039517404084662</v>
+      </c>
+      <c r="C27">
+        <v>95.28149358925523</v>
+      </c>
+      <c r="D27">
+        <v>120.0014935892552</v>
+      </c>
+      <c r="E27">
+        <v>-22.8</v>
+      </c>
+      <c r="F27">
+        <v>28.1</v>
+      </c>
+      <c r="G27">
+        <v>3.38</v>
+      </c>
+      <c r="H27">
+        <v>61.5</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>12</v>
+      </c>
+      <c r="K27">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="L27">
+        <v>11.316</v>
+      </c>
+      <c r="M27">
+        <v>1.43591</v>
+      </c>
+      <c r="N27">
+        <v>9.880090000000001</v>
+      </c>
+      <c r="O27">
+        <v>0.9880089999999999</v>
+      </c>
+      <c r="P27">
+        <v>8.892081000000001</v>
+      </c>
+      <c r="Q27">
+        <v>9.576081</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.1232723205446216</v>
+      </c>
+      <c r="T27">
+        <v>0.9739563617922241</v>
+      </c>
+      <c r="U27">
+        <v>0.0511</v>
+      </c>
+      <c r="V27">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W27">
+        <v>0.04599</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>7.880716758014082</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.104403261700355</v>
+      </c>
+      <c r="C28">
+        <v>93.33157079197903</v>
+      </c>
+      <c r="D28">
+        <v>119.175570791979</v>
+      </c>
+      <c r="E28">
+        <v>-21.67599999999999</v>
+      </c>
+      <c r="F28">
+        <v>29.224</v>
+      </c>
+      <c r="G28">
+        <v>3.38</v>
+      </c>
+      <c r="H28">
+        <v>61.5</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>12</v>
+      </c>
+      <c r="K28">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="L28">
+        <v>11.316</v>
+      </c>
+      <c r="M28">
+        <v>1.548872</v>
+      </c>
+      <c r="N28">
+        <v>9.767128</v>
+      </c>
+      <c r="O28">
+        <v>0.9767127999999997</v>
+      </c>
+      <c r="P28">
+        <v>8.7904152</v>
+      </c>
+      <c r="Q28">
+        <v>9.474415199999999</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.124326029324804</v>
+      </c>
+      <c r="T28">
+        <v>0.9861055055983642</v>
+      </c>
+      <c r="U28">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V28">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W28">
+        <v>0.04770000000000001</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>7.305962016228583</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.1044272829922437</v>
+      </c>
+      <c r="C29">
+        <v>92.16394943449663</v>
+      </c>
+      <c r="D29">
+        <v>119.1319494344966</v>
+      </c>
+      <c r="E29">
+        <v>-20.552</v>
+      </c>
+      <c r="F29">
+        <v>30.348</v>
+      </c>
+      <c r="G29">
+        <v>3.38</v>
+      </c>
+      <c r="H29">
+        <v>61.5</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>12</v>
+      </c>
+      <c r="K29">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="L29">
+        <v>11.316</v>
+      </c>
+      <c r="M29">
+        <v>1.608444</v>
+      </c>
+      <c r="N29">
+        <v>9.707556</v>
+      </c>
+      <c r="O29">
+        <v>0.9707555999999998</v>
+      </c>
+      <c r="P29">
+        <v>8.7368004</v>
+      </c>
+      <c r="Q29">
+        <v>9.420800399999999</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.12540860683869</v>
+      </c>
+      <c r="T29">
+        <v>0.9985875026594669</v>
+      </c>
+      <c r="U29">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V29">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W29">
+        <v>0.04770000000000001</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>7.03537083044234</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.1044513042841325</v>
+      </c>
+      <c r="C30">
+        <v>90.99635999843217</v>
+      </c>
+      <c r="D30">
+        <v>119.0883599984322</v>
+      </c>
+      <c r="E30">
+        <v>-19.42799999999999</v>
+      </c>
+      <c r="F30">
+        <v>31.472</v>
+      </c>
+      <c r="G30">
+        <v>3.38</v>
+      </c>
+      <c r="H30">
+        <v>61.5</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>12</v>
+      </c>
+      <c r="K30">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="L30">
+        <v>11.316</v>
+      </c>
+      <c r="M30">
+        <v>1.668016</v>
+      </c>
+      <c r="N30">
+        <v>9.647984000000001</v>
+      </c>
+      <c r="O30">
+        <v>0.9647983999999998</v>
+      </c>
+      <c r="P30">
+        <v>8.683185600000002</v>
+      </c>
+      <c r="Q30">
+        <v>9.367185600000001</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.126521255950184</v>
+      </c>
+      <c r="T30">
+        <v>1.011416221861156</v>
+      </c>
+      <c r="U30">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V30">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W30">
+        <v>0.04770000000000001</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>6.784107586497971</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.1044753255760212</v>
+      </c>
+      <c r="C31">
+        <v>89.82880244875909</v>
+      </c>
+      <c r="D31">
+        <v>119.0448024487591</v>
+      </c>
+      <c r="E31">
+        <v>-18.304</v>
+      </c>
+      <c r="F31">
+        <v>32.596</v>
+      </c>
+      <c r="G31">
+        <v>3.38</v>
+      </c>
+      <c r="H31">
+        <v>61.5</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>12</v>
+      </c>
+      <c r="K31">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="L31">
+        <v>11.316</v>
+      </c>
+      <c r="M31">
+        <v>1.727588</v>
+      </c>
+      <c r="N31">
+        <v>9.588412000000002</v>
+      </c>
+      <c r="O31">
+        <v>0.9588411999999999</v>
+      </c>
+      <c r="P31">
+        <v>8.629570800000002</v>
+      </c>
+      <c r="Q31">
+        <v>9.313570800000001</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.1276652472901707</v>
+      </c>
+      <c r="T31">
+        <v>1.024606313434723</v>
+      </c>
+      <c r="U31">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V31">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W31">
+        <v>0.04770000000000001</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>6.550172842135973</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.10449934686791</v>
+      </c>
+      <c r="C32">
+        <v>88.66127675050203</v>
+      </c>
+      <c r="D32">
+        <v>119.001276750502</v>
+      </c>
+      <c r="E32">
+        <v>-17.18</v>
+      </c>
+      <c r="F32">
+        <v>33.72</v>
+      </c>
+      <c r="G32">
+        <v>3.38</v>
+      </c>
+      <c r="H32">
+        <v>61.5</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>12</v>
+      </c>
+      <c r="K32">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="L32">
+        <v>11.316</v>
+      </c>
+      <c r="M32">
+        <v>1.78716</v>
+      </c>
+      <c r="N32">
+        <v>9.528840000000001</v>
+      </c>
+      <c r="O32">
+        <v>0.9528839999999998</v>
+      </c>
+      <c r="P32">
+        <v>8.575956000000001</v>
+      </c>
+      <c r="Q32">
+        <v>9.259956000000001</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.1288419240970142</v>
+      </c>
+      <c r="T32">
+        <v>1.038173264767535</v>
+      </c>
+      <c r="U32">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V32">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W32">
+        <v>0.04770000000000001</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>6.331833747398107</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.1050813681597987</v>
+      </c>
+      <c r="C33">
+        <v>86.49231828398763</v>
+      </c>
+      <c r="D33">
+        <v>117.9563182839876</v>
+      </c>
+      <c r="E33">
+        <v>-16.056</v>
+      </c>
+      <c r="F33">
+        <v>34.844</v>
+      </c>
+      <c r="G33">
+        <v>3.38</v>
+      </c>
+      <c r="H33">
+        <v>61.5</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>12</v>
+      </c>
+      <c r="K33">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="L33">
+        <v>11.316</v>
+      </c>
+      <c r="M33">
+        <v>1.91642</v>
+      </c>
+      <c r="N33">
+        <v>9.39958</v>
+      </c>
+      <c r="O33">
+        <v>0.9399579999999998</v>
+      </c>
+      <c r="P33">
+        <v>8.459622</v>
+      </c>
+      <c r="Q33">
+        <v>9.143621999999999</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.1300527074779692</v>
+      </c>
+      <c r="T33">
+        <v>1.052133461066516</v>
+      </c>
+      <c r="U33">
+        <v>0.055</v>
+      </c>
+      <c r="V33">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W33">
+        <v>0.0495</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>5.904759916928439</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.1051233894516875</v>
+      </c>
+      <c r="C34">
+        <v>85.29358330856324</v>
+      </c>
+      <c r="D34">
+        <v>117.8815833085633</v>
+      </c>
+      <c r="E34">
+        <v>-14.932</v>
+      </c>
+      <c r="F34">
+        <v>35.968</v>
+      </c>
+      <c r="G34">
+        <v>3.38</v>
+      </c>
+      <c r="H34">
+        <v>61.5</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>12</v>
+      </c>
+      <c r="K34">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="L34">
+        <v>11.316</v>
+      </c>
+      <c r="M34">
+        <v>1.97824</v>
+      </c>
+      <c r="N34">
+        <v>9.337760000000001</v>
+      </c>
+      <c r="O34">
+        <v>0.9337759999999999</v>
+      </c>
+      <c r="P34">
+        <v>8.403984000000001</v>
+      </c>
+      <c r="Q34">
+        <v>9.087984000000001</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.1312991021348345</v>
+      </c>
+      <c r="T34">
+        <v>1.066504251374291</v>
+      </c>
+      <c r="U34">
+        <v>0.055</v>
+      </c>
+      <c r="V34">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W34">
+        <v>0.0495</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>5.720236169524425</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.1051654107435762</v>
+      </c>
+      <c r="C35">
+        <v>84.0949429746149</v>
+      </c>
+      <c r="D35">
+        <v>117.8069429746149</v>
+      </c>
+      <c r="E35">
+        <v>-13.80799999999999</v>
+      </c>
+      <c r="F35">
+        <v>37.09200000000001</v>
+      </c>
+      <c r="G35">
+        <v>3.38</v>
+      </c>
+      <c r="H35">
+        <v>61.5</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>12</v>
+      </c>
+      <c r="K35">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="L35">
+        <v>11.316</v>
+      </c>
+      <c r="M35">
+        <v>2.04006</v>
+      </c>
+      <c r="N35">
+        <v>9.27594</v>
+      </c>
+      <c r="O35">
+        <v>0.9275939999999998</v>
+      </c>
+      <c r="P35">
+        <v>8.348346000000001</v>
+      </c>
+      <c r="Q35">
+        <v>9.032346</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.1325827026023526</v>
+      </c>
+      <c r="T35">
+        <v>1.081304020497222</v>
+      </c>
+      <c r="U35">
+        <v>0.055</v>
+      </c>
+      <c r="V35">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W35">
+        <v>0.0495</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>5.546895679538836</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.105207432035465</v>
+      </c>
+      <c r="C36">
+        <v>82.89639710248096</v>
+      </c>
+      <c r="D36">
+        <v>117.732397102481</v>
+      </c>
+      <c r="E36">
+        <v>-12.68399999999999</v>
+      </c>
+      <c r="F36">
+        <v>38.21600000000001</v>
+      </c>
+      <c r="G36">
+        <v>3.38</v>
+      </c>
+      <c r="H36">
+        <v>61.5</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>12</v>
+      </c>
+      <c r="K36">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="L36">
+        <v>11.316</v>
+      </c>
+      <c r="M36">
+        <v>2.10188</v>
+      </c>
+      <c r="N36">
+        <v>9.214120000000001</v>
+      </c>
+      <c r="O36">
+        <v>0.9214119999999999</v>
+      </c>
+      <c r="P36">
+        <v>8.292708000000001</v>
+      </c>
+      <c r="Q36">
+        <v>8.976708</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.1339052000537349</v>
+      </c>
+      <c r="T36">
+        <v>1.096552267472364</v>
+      </c>
+      <c r="U36">
+        <v>0.055</v>
+      </c>
+      <c r="V36">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W36">
+        <v>0.0495</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>5.383751688964165</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.1052494533273537</v>
+      </c>
+      <c r="C37">
+        <v>81.69794551295425</v>
+      </c>
+      <c r="D37">
+        <v>117.6579455129543</v>
+      </c>
+      <c r="E37">
+        <v>-11.56</v>
+      </c>
+      <c r="F37">
+        <v>39.34</v>
+      </c>
+      <c r="G37">
+        <v>3.38</v>
+      </c>
+      <c r="H37">
+        <v>61.5</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>12</v>
+      </c>
+      <c r="K37">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="L37">
+        <v>11.316</v>
+      </c>
+      <c r="M37">
+        <v>2.1637</v>
+      </c>
+      <c r="N37">
+        <v>9.1523</v>
+      </c>
+      <c r="O37">
+        <v>0.9152299999999999</v>
+      </c>
+      <c r="P37">
+        <v>8.237070000000001</v>
+      </c>
+      <c r="Q37">
+        <v>8.92107</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.1352683897343904</v>
+      </c>
+      <c r="T37">
+        <v>1.11226969127751</v>
+      </c>
+      <c r="U37">
+        <v>0.055</v>
+      </c>
+      <c r="V37">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W37">
+        <v>0.0495</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>5.229930212136617</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.1052914746192425</v>
+      </c>
+      <c r="C38">
+        <v>80.4995880272804</v>
+      </c>
+      <c r="D38">
+        <v>117.5835880272804</v>
+      </c>
+      <c r="E38">
+        <v>-10.436</v>
+      </c>
+      <c r="F38">
+        <v>40.464</v>
+      </c>
+      <c r="G38">
+        <v>3.38</v>
+      </c>
+      <c r="H38">
+        <v>61.5</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>12</v>
+      </c>
+      <c r="K38">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="L38">
+        <v>11.316</v>
+      </c>
+      <c r="M38">
+        <v>2.22552</v>
+      </c>
+      <c r="N38">
+        <v>9.090480000000001</v>
+      </c>
+      <c r="O38">
+        <v>0.909048</v>
+      </c>
+      <c r="P38">
+        <v>8.181432000000001</v>
+      </c>
+      <c r="Q38">
+        <v>8.865432</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.1366741790925664</v>
+      </c>
+      <c r="T38">
+        <v>1.128478284576567</v>
+      </c>
+      <c r="U38">
+        <v>0.055</v>
+      </c>
+      <c r="V38">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W38">
+        <v>0.0495</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>5.084654372910602</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.1053334959111312</v>
+      </c>
+      <c r="C39">
+        <v>79.30132446715695</v>
+      </c>
+      <c r="D39">
+        <v>117.509324467157</v>
+      </c>
+      <c r="E39">
+        <v>-9.311999999999998</v>
+      </c>
+      <c r="F39">
+        <v>41.588</v>
+      </c>
+      <c r="G39">
+        <v>3.38</v>
+      </c>
+      <c r="H39">
+        <v>61.5</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>12</v>
+      </c>
+      <c r="K39">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="L39">
+        <v>11.316</v>
+      </c>
+      <c r="M39">
+        <v>2.28734</v>
+      </c>
+      <c r="N39">
+        <v>9.02866</v>
+      </c>
+      <c r="O39">
+        <v>0.9028659999999998</v>
+      </c>
+      <c r="P39">
+        <v>8.125794000000001</v>
+      </c>
+      <c r="Q39">
+        <v>8.809794</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.1381245966843353</v>
+      </c>
+      <c r="T39">
+        <v>1.145201436393054</v>
+      </c>
+      <c r="U39">
+        <v>0.055</v>
+      </c>
+      <c r="V39">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W39">
+        <v>0.0495</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>4.947231281750855</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.10537551720302</v>
+      </c>
+      <c r="C40">
+        <v>78.10315465473136</v>
+      </c>
+      <c r="D40">
+        <v>117.4351546547314</v>
+      </c>
+      <c r="E40">
+        <v>-8.187999999999995</v>
+      </c>
+      <c r="F40">
+        <v>42.712</v>
+      </c>
+      <c r="G40">
+        <v>3.38</v>
+      </c>
+      <c r="H40">
+        <v>61.5</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>12</v>
+      </c>
+      <c r="K40">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="L40">
+        <v>11.316</v>
+      </c>
+      <c r="M40">
+        <v>2.34916</v>
+      </c>
+      <c r="N40">
+        <v>8.966840000000001</v>
+      </c>
+      <c r="O40">
+        <v>0.8966839999999999</v>
+      </c>
+      <c r="P40">
+        <v>8.070156000000001</v>
+      </c>
+      <c r="Q40">
+        <v>8.754156</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.1396218019403548</v>
+      </c>
+      <c r="T40">
+        <v>1.162464044719751</v>
+      </c>
+      <c r="U40">
+        <v>0.055</v>
+      </c>
+      <c r="V40">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W40">
+        <v>0.0495</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>4.817040984862674</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.1054175384949088</v>
+      </c>
+      <c r="C41">
+        <v>76.90507841259992</v>
+      </c>
+      <c r="D41">
+        <v>117.3610784125999</v>
+      </c>
+      <c r="E41">
+        <v>-7.063999999999993</v>
+      </c>
+      <c r="F41">
+        <v>43.83600000000001</v>
+      </c>
+      <c r="G41">
+        <v>3.38</v>
+      </c>
+      <c r="H41">
+        <v>61.5</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>12</v>
+      </c>
+      <c r="K41">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="L41">
+        <v>11.316</v>
+      </c>
+      <c r="M41">
+        <v>2.41098</v>
+      </c>
+      <c r="N41">
+        <v>8.90502</v>
+      </c>
+      <c r="O41">
+        <v>0.8905019999999998</v>
+      </c>
+      <c r="P41">
+        <v>8.014518000000001</v>
+      </c>
+      <c r="Q41">
+        <v>8.698518</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.141168095893293</v>
+      </c>
+      <c r="T41">
+        <v>1.1802926402047</v>
+      </c>
+      <c r="U41">
+        <v>0.055</v>
+      </c>
+      <c r="V41">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W41">
+        <v>0.0495</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>4.693527113455939</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.1054595597867975</v>
+      </c>
+      <c r="C42">
+        <v>75.70709556380635</v>
+      </c>
+      <c r="D42">
+        <v>117.2870955638064</v>
+      </c>
+      <c r="E42">
+        <v>-5.939999999999991</v>
+      </c>
+      <c r="F42">
+        <v>44.96000000000001</v>
+      </c>
+      <c r="G42">
+        <v>3.38</v>
+      </c>
+      <c r="H42">
+        <v>61.5</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>12</v>
+      </c>
+      <c r="K42">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="L42">
+        <v>11.316</v>
+      </c>
+      <c r="M42">
+        <v>2.4728</v>
+      </c>
+      <c r="N42">
+        <v>8.8432</v>
+      </c>
+      <c r="O42">
+        <v>0.8843199999999998</v>
+      </c>
+      <c r="P42">
+        <v>7.95888</v>
+      </c>
+      <c r="Q42">
+        <v>8.64288</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.1427659329779958</v>
+      </c>
+      <c r="T42">
+        <v>1.198715522205814</v>
+      </c>
+      <c r="U42">
+        <v>0.055</v>
+      </c>
+      <c r="V42">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W42">
+        <v>0.0495</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>4.576188935619539</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.1069037810786863</v>
+      </c>
+      <c r="C43">
+        <v>72.09588387020992</v>
+      </c>
+      <c r="D43">
+        <v>114.7998838702099</v>
+      </c>
+      <c r="E43">
+        <v>-4.815999999999995</v>
+      </c>
+      <c r="F43">
+        <v>46.084</v>
+      </c>
+      <c r="G43">
+        <v>3.38</v>
+      </c>
+      <c r="H43">
+        <v>61.5</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>12</v>
+      </c>
+      <c r="K43">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="L43">
+        <v>11.316</v>
+      </c>
+      <c r="M43">
+        <v>2.7097392</v>
+      </c>
+      <c r="N43">
+        <v>8.606260800000001</v>
+      </c>
+      <c r="O43">
+        <v>0.86062608</v>
+      </c>
+      <c r="P43">
+        <v>7.745634720000001</v>
+      </c>
+      <c r="Q43">
+        <v>8.429634720000001</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.1444179340316716</v>
+      </c>
+      <c r="T43">
+        <v>1.217762908681542</v>
+      </c>
+      <c r="U43">
+        <v>0.05880000000000001</v>
+      </c>
+      <c r="V43">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W43">
+        <v>0.05292000000000001</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>4.176047643256591</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.106980002370575</v>
+      </c>
+      <c r="C44">
+        <v>70.84354425224234</v>
+      </c>
+      <c r="D44">
+        <v>114.6715442522423</v>
+      </c>
+      <c r="E44">
+        <v>-3.692</v>
+      </c>
+      <c r="F44">
+        <v>47.208</v>
+      </c>
+      <c r="G44">
+        <v>3.38</v>
+      </c>
+      <c r="H44">
+        <v>61.5</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>12</v>
+      </c>
+      <c r="K44">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="L44">
+        <v>11.316</v>
+      </c>
+      <c r="M44">
+        <v>2.7758304</v>
+      </c>
+      <c r="N44">
+        <v>8.5401696</v>
+      </c>
+      <c r="O44">
+        <v>0.8540169599999998</v>
+      </c>
+      <c r="P44">
+        <v>7.68615264</v>
+      </c>
+      <c r="Q44">
+        <v>8.370152640000001</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.1461269006389224</v>
+      </c>
+      <c r="T44">
+        <v>1.237467101587468</v>
+      </c>
+      <c r="U44">
+        <v>0.05880000000000001</v>
+      </c>
+      <c r="V44">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W44">
+        <v>0.05292000000000001</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>4.076617937464768</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.1086816236624638</v>
+      </c>
+      <c r="C45">
+        <v>66.92728598680955</v>
+      </c>
+      <c r="D45">
+        <v>111.8792859868095</v>
+      </c>
+      <c r="E45">
+        <v>-2.567999999999998</v>
+      </c>
+      <c r="F45">
+        <v>48.332</v>
+      </c>
+      <c r="G45">
+        <v>3.38</v>
+      </c>
+      <c r="H45">
+        <v>61.5</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>12</v>
+      </c>
+      <c r="K45">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="L45">
+        <v>11.316</v>
+      </c>
+      <c r="M45">
+        <v>3.044916</v>
+      </c>
+      <c r="N45">
+        <v>8.271084</v>
+      </c>
+      <c r="O45">
+        <v>0.8271083999999999</v>
+      </c>
+      <c r="P45">
+        <v>7.4439756</v>
+      </c>
+      <c r="Q45">
+        <v>8.127975599999999</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.1478958309867785</v>
+      </c>
+      <c r="T45">
+        <v>1.257862669683075</v>
+      </c>
+      <c r="U45">
+        <v>0.063</v>
+      </c>
+      <c r="V45">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W45">
+        <v>0.0567</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>3.716358677874858</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.1087956449543525</v>
+      </c>
+      <c r="C46">
+        <v>65.62103720930165</v>
+      </c>
+      <c r="D46">
+        <v>111.6970372093017</v>
+      </c>
+      <c r="E46">
+        <v>-1.443999999999996</v>
+      </c>
+      <c r="F46">
+        <v>49.456</v>
+      </c>
+      <c r="G46">
+        <v>3.38</v>
+      </c>
+      <c r="H46">
+        <v>61.5</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>12</v>
+      </c>
+      <c r="K46">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="L46">
+        <v>11.316</v>
+      </c>
+      <c r="M46">
+        <v>3.115728</v>
+      </c>
+      <c r="N46">
+        <v>8.200272</v>
+      </c>
+      <c r="O46">
+        <v>0.8200271999999998</v>
+      </c>
+      <c r="P46">
+        <v>7.3802448</v>
+      </c>
+      <c r="Q46">
+        <v>8.064244799999999</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.1497279374184866</v>
+      </c>
+      <c r="T46">
+        <v>1.278986650924954</v>
+      </c>
+      <c r="U46">
+        <v>0.063</v>
+      </c>
+      <c r="V46">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W46">
+        <v>0.0567</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>3.631895980650429</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.1089096662462413</v>
+      </c>
+      <c r="C47">
+        <v>64.31538122426221</v>
+      </c>
+      <c r="D47">
+        <v>111.5153812242622</v>
+      </c>
+      <c r="E47">
+        <v>-0.3199999999999932</v>
+      </c>
+      <c r="F47">
+        <v>50.58000000000001</v>
+      </c>
+      <c r="G47">
+        <v>3.38</v>
+      </c>
+      <c r="H47">
+        <v>61.5</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>12</v>
+      </c>
+      <c r="K47">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="L47">
+        <v>11.316</v>
+      </c>
+      <c r="M47">
+        <v>3.18654</v>
+      </c>
+      <c r="N47">
+        <v>8.12946</v>
+      </c>
+      <c r="O47">
+        <v>0.8129459999999998</v>
+      </c>
+      <c r="P47">
+        <v>7.316514</v>
+      </c>
+      <c r="Q47">
+        <v>8.000513999999999</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.1516266659022568</v>
+      </c>
+      <c r="T47">
+        <v>1.300878776939264</v>
+      </c>
+      <c r="U47">
+        <v>0.063</v>
+      </c>
+      <c r="V47">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W47">
+        <v>0.0567</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>3.551187181080419</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.11196308753813</v>
+      </c>
+      <c r="C48">
+        <v>58.53734801078144</v>
+      </c>
+      <c r="D48">
+        <v>106.8613480107815</v>
+      </c>
+      <c r="E48">
+        <v>0.8040000000000092</v>
+      </c>
+      <c r="F48">
+        <v>51.70400000000001</v>
+      </c>
+      <c r="G48">
+        <v>3.38</v>
+      </c>
+      <c r="H48">
+        <v>61.5</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>12</v>
+      </c>
+      <c r="K48">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="L48">
+        <v>11.316</v>
+      </c>
+      <c r="M48">
+        <v>3.6244504</v>
+      </c>
+      <c r="N48">
+        <v>7.6915496</v>
+      </c>
+      <c r="O48">
+        <v>0.7691549599999998</v>
+      </c>
+      <c r="P48">
+        <v>6.92239464</v>
+      </c>
+      <c r="Q48">
+        <v>7.60639464</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.1535957176632037</v>
+      </c>
+      <c r="T48">
+        <v>1.323581722435587</v>
+      </c>
+      <c r="U48">
+        <v>0.0701</v>
+      </c>
+      <c r="V48">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W48">
+        <v>0.06308999999999999</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>3.122128530162807</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.1121410088300188</v>
+      </c>
+      <c r="C49">
+        <v>57.15410820218931</v>
+      </c>
+      <c r="D49">
+        <v>106.6021082021893</v>
+      </c>
+      <c r="E49">
+        <v>1.928000000000004</v>
+      </c>
+      <c r="F49">
+        <v>52.828</v>
+      </c>
+      <c r="G49">
+        <v>3.38</v>
+      </c>
+      <c r="H49">
+        <v>61.5</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>12</v>
+      </c>
+      <c r="K49">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="L49">
+        <v>11.316</v>
+      </c>
+      <c r="M49">
+        <v>3.7032428</v>
+      </c>
+      <c r="N49">
+        <v>7.612757200000001</v>
+      </c>
+      <c r="O49">
+        <v>0.7612757199999999</v>
+      </c>
+      <c r="P49">
+        <v>6.851481480000001</v>
+      </c>
+      <c r="Q49">
+        <v>7.535481480000001</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.1556390732641864</v>
+      </c>
+      <c r="T49">
+        <v>1.347141382856298</v>
+      </c>
+      <c r="U49">
+        <v>0.0701</v>
+      </c>
+      <c r="V49">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W49">
+        <v>0.06308999999999999</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>3.055700263563599</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.1215205301219075</v>
+      </c>
+      <c r="C50">
+        <v>43.94270085398786</v>
+      </c>
+      <c r="D50">
+        <v>94.51470085398786</v>
+      </c>
+      <c r="E50">
+        <v>3.052</v>
+      </c>
+      <c r="F50">
+        <v>53.952</v>
+      </c>
+      <c r="G50">
+        <v>3.38</v>
+      </c>
+      <c r="H50">
+        <v>61.5</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>12</v>
+      </c>
+      <c r="K50">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="L50">
+        <v>11.316</v>
+      </c>
+      <c r="M50">
+        <v>4.9312128</v>
+      </c>
+      <c r="N50">
+        <v>6.384787200000001</v>
+      </c>
+      <c r="O50">
+        <v>0.6384787199999999</v>
+      </c>
+      <c r="P50">
+        <v>5.746308480000001</v>
+      </c>
+      <c r="Q50">
+        <v>6.430308480000001</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.1577610194652068</v>
+      </c>
+      <c r="T50">
+        <v>1.371607184062422</v>
+      </c>
+      <c r="U50">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V50">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W50">
+        <v>0.08226000000000001</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>2.294770162828909</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.1218901514137963</v>
+      </c>
+      <c r="C51">
+        <v>42.3982581753104</v>
+      </c>
+      <c r="D51">
+        <v>94.0942581753104</v>
+      </c>
+      <c r="E51">
+        <v>4.176000000000002</v>
+      </c>
+      <c r="F51">
+        <v>55.076</v>
+      </c>
+      <c r="G51">
+        <v>3.38</v>
+      </c>
+      <c r="H51">
+        <v>61.5</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>12</v>
+      </c>
+      <c r="K51">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="L51">
+        <v>11.316</v>
+      </c>
+      <c r="M51">
+        <v>5.0339464</v>
+      </c>
+      <c r="N51">
+        <v>6.2820536</v>
+      </c>
+      <c r="O51">
+        <v>0.6282053599999999</v>
+      </c>
+      <c r="P51">
+        <v>5.65384824</v>
+      </c>
+      <c r="Q51">
+        <v>6.33784824</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.1599661792427378</v>
+      </c>
+      <c r="T51">
+        <v>1.3970324284531</v>
+      </c>
+      <c r="U51">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V51">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W51">
+        <v>0.08226000000000001</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>2.247938118689543</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.122259772705685</v>
+      </c>
+      <c r="C52">
+        <v>40.85753955580591</v>
+      </c>
+      <c r="D52">
+        <v>93.67753955580592</v>
+      </c>
+      <c r="E52">
+        <v>5.300000000000004</v>
+      </c>
+      <c r="F52">
+        <v>56.2</v>
+      </c>
+      <c r="G52">
+        <v>3.38</v>
+      </c>
+      <c r="H52">
+        <v>61.5</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>12</v>
+      </c>
+      <c r="K52">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="L52">
+        <v>11.316</v>
+      </c>
+      <c r="M52">
+        <v>5.136680000000001</v>
+      </c>
+      <c r="N52">
+        <v>6.17932</v>
+      </c>
+      <c r="O52">
+        <v>0.6179319999999998</v>
+      </c>
+      <c r="P52">
+        <v>5.561388</v>
+      </c>
+      <c r="Q52">
+        <v>6.245388</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.1622595454113701</v>
+      </c>
+      <c r="T52">
+        <v>1.423474682619404</v>
+      </c>
+      <c r="U52">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V52">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W52">
+        <v>0.08226000000000001</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>2.202979356315752</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.1226293939975738</v>
+      </c>
+      <c r="C53">
+        <v>39.32049573501224</v>
+      </c>
+      <c r="D53">
+        <v>93.26449573501225</v>
+      </c>
+      <c r="E53">
+        <v>6.424000000000007</v>
+      </c>
+      <c r="F53">
+        <v>57.32400000000001</v>
+      </c>
+      <c r="G53">
+        <v>3.38</v>
+      </c>
+      <c r="H53">
+        <v>61.5</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>12</v>
+      </c>
+      <c r="K53">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="L53">
+        <v>11.316</v>
+      </c>
+      <c r="M53">
+        <v>5.239413600000001</v>
+      </c>
+      <c r="N53">
+        <v>6.0765864</v>
+      </c>
+      <c r="O53">
+        <v>0.6076586399999999</v>
+      </c>
+      <c r="P53">
+        <v>5.46892776</v>
+      </c>
+      <c r="Q53">
+        <v>6.15292776</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.1646465183623955</v>
+      </c>
+      <c r="T53">
+        <v>1.450996212465966</v>
+      </c>
+      <c r="U53">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V53">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W53">
+        <v>0.08226000000000001</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>2.159783682662503</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.1229990152894625</v>
+      </c>
+      <c r="C54">
+        <v>37.78707831745199</v>
+      </c>
+      <c r="D54">
+        <v>92.855078317452</v>
+      </c>
+      <c r="E54">
+        <v>7.548000000000009</v>
+      </c>
+      <c r="F54">
+        <v>58.44800000000001</v>
+      </c>
+      <c r="G54">
+        <v>3.38</v>
+      </c>
+      <c r="H54">
+        <v>61.5</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>12</v>
+      </c>
+      <c r="K54">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="L54">
+        <v>11.316</v>
+      </c>
+      <c r="M54">
+        <v>5.342147200000001</v>
+      </c>
+      <c r="N54">
+        <v>5.9738528</v>
+      </c>
+      <c r="O54">
+        <v>0.5973852799999998</v>
+      </c>
+      <c r="P54">
+        <v>5.376467519999999</v>
+      </c>
+      <c r="Q54">
+        <v>6.06046752</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.1671329485197136</v>
+      </c>
+      <c r="T54">
+        <v>1.479664472722802</v>
+      </c>
+      <c r="U54">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V54">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W54">
+        <v>0.08226000000000001</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>2.118249381072839</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.1233686365813513</v>
+      </c>
+      <c r="C55">
+        <v>36.25723975372969</v>
+      </c>
+      <c r="D55">
+        <v>92.4492397537297</v>
+      </c>
+      <c r="E55">
+        <v>8.672000000000004</v>
+      </c>
+      <c r="F55">
+        <v>59.572</v>
+      </c>
+      <c r="G55">
+        <v>3.38</v>
+      </c>
+      <c r="H55">
+        <v>61.5</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>12</v>
+      </c>
+      <c r="K55">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="L55">
+        <v>11.316</v>
+      </c>
+      <c r="M55">
+        <v>5.444880800000001</v>
+      </c>
+      <c r="N55">
+        <v>5.8711192</v>
+      </c>
+      <c r="O55">
+        <v>0.5871119199999999</v>
+      </c>
+      <c r="P55">
+        <v>5.28400728</v>
+      </c>
+      <c r="Q55">
+        <v>5.96800728</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.169725184215641</v>
+      </c>
+      <c r="T55">
+        <v>1.509552658948013</v>
+      </c>
+      <c r="U55">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V55">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W55">
+        <v>0.08226000000000001</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>2.078282411618634</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.1237382578732401</v>
+      </c>
+      <c r="C56">
+        <v>34.73093332212257</v>
+      </c>
+      <c r="D56">
+        <v>92.04693332212258</v>
+      </c>
+      <c r="E56">
+        <v>9.796000000000006</v>
+      </c>
+      <c r="F56">
+        <v>60.69600000000001</v>
+      </c>
+      <c r="G56">
+        <v>3.38</v>
+      </c>
+      <c r="H56">
+        <v>61.5</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>12</v>
+      </c>
+      <c r="K56">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="L56">
+        <v>11.316</v>
+      </c>
+      <c r="M56">
+        <v>5.547614400000001</v>
+      </c>
+      <c r="N56">
+        <v>5.768385599999999</v>
+      </c>
+      <c r="O56">
+        <v>0.5768385599999998</v>
+      </c>
+      <c r="P56">
+        <v>5.19154704</v>
+      </c>
+      <c r="Q56">
+        <v>5.87554704</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.1724301258113914</v>
+      </c>
+      <c r="T56">
+        <v>1.540740331530843</v>
+      </c>
+      <c r="U56">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V56">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W56">
+        <v>0.08226000000000001</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>2.039795700292363</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.1241078791651288</v>
+      </c>
+      <c r="C57">
+        <v>33.20811311064992</v>
+      </c>
+      <c r="D57">
+        <v>91.64811311064993</v>
+      </c>
+      <c r="E57">
+        <v>10.92000000000001</v>
+      </c>
+      <c r="F57">
+        <v>61.82000000000001</v>
+      </c>
+      <c r="G57">
+        <v>3.38</v>
+      </c>
+      <c r="H57">
+        <v>61.5</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>12</v>
+      </c>
+      <c r="K57">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="L57">
+        <v>11.316</v>
+      </c>
+      <c r="M57">
+        <v>5.650348000000001</v>
+      </c>
+      <c r="N57">
+        <v>5.665652</v>
+      </c>
+      <c r="O57">
+        <v>0.5665651999999999</v>
+      </c>
+      <c r="P57">
+        <v>5.0990868</v>
+      </c>
+      <c r="Q57">
+        <v>5.7830868</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.1752552870336196</v>
+      </c>
+      <c r="T57">
+        <v>1.573314122895132</v>
+      </c>
+      <c r="U57">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V57">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W57">
+        <v>0.08226000000000001</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>2.002708505741593</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.1351119004570175</v>
+      </c>
+      <c r="C58">
+        <v>21.6129482468531</v>
+      </c>
+      <c r="D58">
+        <v>81.17694824685312</v>
+      </c>
+      <c r="E58">
+        <v>12.04400000000001</v>
+      </c>
+      <c r="F58">
+        <v>62.94400000000001</v>
+      </c>
+      <c r="G58">
+        <v>3.38</v>
+      </c>
+      <c r="H58">
+        <v>61.5</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>12</v>
+      </c>
+      <c r="K58">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="L58">
+        <v>11.316</v>
+      </c>
+      <c r="M58">
+        <v>7.081200000000001</v>
+      </c>
+      <c r="N58">
+        <v>4.2348</v>
+      </c>
+      <c r="O58">
+        <v>0.4234799999999999</v>
+      </c>
+      <c r="P58">
+        <v>3.81132</v>
+      </c>
+      <c r="Q58">
+        <v>4.49532</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.1782088646750399</v>
+      </c>
+      <c r="T58">
+        <v>1.607368541139615</v>
+      </c>
+      <c r="U58">
+        <v>0.1125</v>
+      </c>
+      <c r="V58">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W58">
+        <v>0.10125</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>1.598034231486189</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.1356714217489063</v>
+      </c>
+      <c r="C59">
+        <v>20.02007693130251</v>
+      </c>
+      <c r="D59">
+        <v>80.70807693130253</v>
+      </c>
+      <c r="E59">
+        <v>13.16800000000001</v>
+      </c>
+      <c r="F59">
+        <v>64.06800000000001</v>
+      </c>
+      <c r="G59">
+        <v>3.38</v>
+      </c>
+      <c r="H59">
+        <v>61.5</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>12</v>
+      </c>
+      <c r="K59">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="L59">
+        <v>11.316</v>
+      </c>
+      <c r="M59">
+        <v>7.207650000000002</v>
+      </c>
+      <c r="N59">
+        <v>4.108349999999999</v>
+      </c>
+      <c r="O59">
+        <v>0.4108349999999998</v>
+      </c>
+      <c r="P59">
+        <v>3.697514999999999</v>
+      </c>
+      <c r="Q59">
+        <v>4.381514999999999</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.1812998180207123</v>
+      </c>
+      <c r="T59">
+        <v>1.643006885814074</v>
+      </c>
+      <c r="U59">
+        <v>0.1125</v>
+      </c>
+      <c r="V59">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W59">
+        <v>0.10125</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>1.569998543214501</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.1362309430407951</v>
+      </c>
+      <c r="C60">
+        <v>18.43259083478027</v>
+      </c>
+      <c r="D60">
+        <v>80.24459083478027</v>
+      </c>
+      <c r="E60">
+        <v>14.29199999999999</v>
+      </c>
+      <c r="F60">
+        <v>65.19199999999999</v>
+      </c>
+      <c r="G60">
+        <v>3.38</v>
+      </c>
+      <c r="H60">
+        <v>61.5</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>12</v>
+      </c>
+      <c r="K60">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="L60">
+        <v>11.316</v>
+      </c>
+      <c r="M60">
+        <v>7.334099999999999</v>
+      </c>
+      <c r="N60">
+        <v>3.981900000000001</v>
+      </c>
+      <c r="O60">
+        <v>0.39819</v>
+      </c>
+      <c r="P60">
+        <v>3.583710000000001</v>
+      </c>
+      <c r="Q60">
+        <v>4.267710000000001</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.1845379596209406</v>
+      </c>
+      <c r="T60">
+        <v>1.68034229452065</v>
+      </c>
+      <c r="U60">
+        <v>0.1125</v>
+      </c>
+      <c r="V60">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W60">
+        <v>0.10125</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>1.542929602814251</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.1367904643326838</v>
+      </c>
+      <c r="C61">
+        <v>16.85039770918667</v>
+      </c>
+      <c r="D61">
+        <v>79.78639770918667</v>
+      </c>
+      <c r="E61">
+        <v>15.416</v>
+      </c>
+      <c r="F61">
+        <v>66.316</v>
+      </c>
+      <c r="G61">
+        <v>3.38</v>
+      </c>
+      <c r="H61">
+        <v>61.5</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>12</v>
+      </c>
+      <c r="K61">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="L61">
+        <v>11.316</v>
+      </c>
+      <c r="M61">
+        <v>7.46055</v>
+      </c>
+      <c r="N61">
+        <v>3.85545</v>
+      </c>
+      <c r="O61">
+        <v>0.3855449999999999</v>
+      </c>
+      <c r="P61">
+        <v>3.469905</v>
+      </c>
+      <c r="Q61">
+        <v>4.153905</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.1879340593480092</v>
+      </c>
+      <c r="T61">
+        <v>1.719498942676328</v>
+      </c>
+      <c r="U61">
+        <v>0.1125</v>
+      </c>
+      <c r="V61">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W61">
+        <v>0.10125</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>1.51677825361401</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.1850636221617298</v>
+      </c>
+      <c r="C62">
+        <v>-10.60647516994791</v>
+      </c>
+      <c r="D62">
+        <v>53.45352483005208</v>
+      </c>
+      <c r="E62">
+        <v>16.54</v>
+      </c>
+      <c r="F62">
+        <v>67.44</v>
+      </c>
+      <c r="G62">
+        <v>3.38</v>
+      </c>
+      <c r="H62">
+        <v>61.5</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>12</v>
+      </c>
+      <c r="K62">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="L62">
+        <v>11.316</v>
+      </c>
+      <c r="M62">
+        <v>13.258704</v>
+      </c>
+      <c r="N62">
+        <v>-1.942703999999999</v>
+      </c>
+      <c r="O62">
+        <v>-0.1942703999999999</v>
+      </c>
+      <c r="P62">
+        <v>-1.748433599999999</v>
+      </c>
+      <c r="Q62">
+        <v>-1.064433599999999</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.192928094550232</v>
+      </c>
+      <c r="T62">
+        <v>1.777079607263964</v>
+      </c>
+      <c r="U62">
+        <v>0.1966</v>
+      </c>
+      <c r="V62">
+        <v>0.0853477081922939</v>
+      </c>
+      <c r="W62">
+        <v>0.179820640569395</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>0.8534770819229391</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.1866416221617298</v>
+      </c>
+      <c r="C63">
+        <v>-12.30101586713771</v>
+      </c>
+      <c r="D63">
+        <v>52.8829841328623</v>
+      </c>
+      <c r="E63">
+        <v>17.66400000000001</v>
+      </c>
+      <c r="F63">
+        <v>68.56400000000001</v>
+      </c>
+      <c r="G63">
+        <v>3.38</v>
+      </c>
+      <c r="H63">
+        <v>61.5</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>12</v>
+      </c>
+      <c r="K63">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="L63">
+        <v>11.316</v>
+      </c>
+      <c r="M63">
+        <v>13.4796824</v>
+      </c>
+      <c r="N63">
+        <v>-2.163682400000001</v>
+      </c>
+      <c r="O63">
+        <v>-0.21636824</v>
+      </c>
+      <c r="P63">
+        <v>-1.947314160000001</v>
+      </c>
+      <c r="Q63">
+        <v>-1.263314160000001</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.196880096974597</v>
+      </c>
+      <c r="T63">
+        <v>1.822645751039964</v>
+      </c>
+      <c r="U63">
+        <v>0.1966</v>
+      </c>
+      <c r="V63">
+        <v>0.08394856543504317</v>
+      </c>
+      <c r="W63">
+        <v>0.1800957120354705</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>0.8394856543504319</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.1882196221617298</v>
+      </c>
+      <c r="C64">
+        <v>-13.98350576126507</v>
+      </c>
+      <c r="D64">
+        <v>52.32449423873493</v>
+      </c>
+      <c r="E64">
+        <v>18.788</v>
+      </c>
+      <c r="F64">
+        <v>69.688</v>
+      </c>
+      <c r="G64">
+        <v>3.38</v>
+      </c>
+      <c r="H64">
+        <v>61.5</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>12</v>
+      </c>
+      <c r="K64">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="L64">
+        <v>11.316</v>
+      </c>
+      <c r="M64">
+        <v>13.7006608</v>
+      </c>
+      <c r="N64">
+        <v>-2.384660799999999</v>
+      </c>
+      <c r="O64">
+        <v>-0.2384660799999998</v>
+      </c>
+      <c r="P64">
+        <v>-2.146194719999999</v>
+      </c>
+      <c r="Q64">
+        <v>-1.462194719999999</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.20104009952656</v>
+      </c>
+      <c r="T64">
+        <v>1.870610112909436</v>
+      </c>
+      <c r="U64">
+        <v>0.1966</v>
+      </c>
+      <c r="V64">
+        <v>0.08259455631512312</v>
+      </c>
+      <c r="W64">
+        <v>0.1803619102284468</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>0.8259455631512315</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.1897976221617299</v>
+      </c>
+      <c r="C65">
+        <v>-15.65432266292653</v>
+      </c>
+      <c r="D65">
+        <v>51.77767733707346</v>
+      </c>
+      <c r="E65">
+        <v>19.912</v>
+      </c>
+      <c r="F65">
+        <v>70.812</v>
+      </c>
+      <c r="G65">
+        <v>3.38</v>
+      </c>
+      <c r="H65">
+        <v>61.5</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>12</v>
+      </c>
+      <c r="K65">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="L65">
+        <v>11.316</v>
+      </c>
+      <c r="M65">
+        <v>13.9216392</v>
+      </c>
+      <c r="N65">
+        <v>-2.605639199999999</v>
+      </c>
+      <c r="O65">
+        <v>-0.2605639199999998</v>
+      </c>
+      <c r="P65">
+        <v>-2.345075279999999</v>
+      </c>
+      <c r="Q65">
+        <v>-1.661075279999999</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.2054249670813319</v>
+      </c>
+      <c r="T65">
+        <v>1.92116714298807</v>
+      </c>
+      <c r="U65">
+        <v>0.1966</v>
+      </c>
+      <c r="V65">
+        <v>0.08128353161170847</v>
+      </c>
+      <c r="W65">
+        <v>0.1806196576851381</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>0.8128353161170849</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.1913756221617298</v>
+      </c>
+      <c r="C66">
+        <v>-17.31382875282662</v>
+      </c>
+      <c r="D66">
+        <v>51.24217124717339</v>
+      </c>
+      <c r="E66">
+        <v>21.03600000000001</v>
+      </c>
+      <c r="F66">
+        <v>71.93600000000001</v>
+      </c>
+      <c r="G66">
+        <v>3.38</v>
+      </c>
+      <c r="H66">
+        <v>61.5</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>12</v>
+      </c>
+      <c r="K66">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="L66">
+        <v>11.316</v>
+      </c>
+      <c r="M66">
+        <v>14.1426176</v>
+      </c>
+      <c r="N66">
+        <v>-2.826617600000001</v>
+      </c>
+      <c r="O66">
+        <v>-0.28266176</v>
+      </c>
+      <c r="P66">
+        <v>-2.543955840000001</v>
+      </c>
+      <c r="Q66">
+        <v>-1.85995584</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.2100534383891467</v>
+      </c>
+      <c r="T66">
+        <v>1.97453289695996</v>
+      </c>
+      <c r="U66">
+        <v>0.1966</v>
+      </c>
+      <c r="V66">
+        <v>0.08001347643027551</v>
+      </c>
+      <c r="W66">
+        <v>0.1808693505338078</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>0.8001347643027554</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.2044013138783241</v>
+      </c>
+      <c r="C67">
+        <v>-22.46838086574665</v>
+      </c>
+      <c r="D67">
+        <v>47.21161913425335</v>
+      </c>
+      <c r="E67">
+        <v>22.16</v>
+      </c>
+      <c r="F67">
+        <v>73.06</v>
+      </c>
+      <c r="G67">
+        <v>3.38</v>
+      </c>
+      <c r="H67">
+        <v>61.5</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>12</v>
+      </c>
+      <c r="K67">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="L67">
+        <v>11.316</v>
+      </c>
+      <c r="M67">
+        <v>15.620228</v>
+      </c>
+      <c r="N67">
+        <v>-4.304227999999998</v>
+      </c>
+      <c r="O67">
+        <v>-0.4304227999999997</v>
+      </c>
+      <c r="P67">
+        <v>-3.873805199999999</v>
+      </c>
+      <c r="Q67">
+        <v>-3.189805199999999</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.2157112272476774</v>
+      </c>
+      <c r="T67">
+        <v>2.039766566603644</v>
+      </c>
+      <c r="U67">
+        <v>0.2138</v>
+      </c>
+      <c r="V67">
+        <v>0.07244452513753319</v>
+      </c>
+      <c r="W67">
+        <v>0.1983113605255954</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>0.7244452513753321</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.2061513138783241</v>
+      </c>
+      <c r="C68">
+        <v>-24.08607482948222</v>
+      </c>
+      <c r="D68">
+        <v>46.71792517051779</v>
+      </c>
+      <c r="E68">
+        <v>23.28400000000001</v>
+      </c>
+      <c r="F68">
+        <v>74.18400000000001</v>
+      </c>
+      <c r="G68">
+        <v>3.38</v>
+      </c>
+      <c r="H68">
+        <v>61.5</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>12</v>
+      </c>
+      <c r="K68">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="L68">
+        <v>11.316</v>
+      </c>
+      <c r="M68">
+        <v>15.8605392</v>
+      </c>
+      <c r="N68">
+        <v>-4.544539200000001</v>
+      </c>
+      <c r="O68">
+        <v>-0.45445392</v>
+      </c>
+      <c r="P68">
+        <v>-4.090085280000001</v>
+      </c>
+      <c r="Q68">
+        <v>-3.406085280000001</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.220914498637315</v>
+      </c>
+      <c r="T68">
+        <v>2.099759700915516</v>
+      </c>
+      <c r="U68">
+        <v>0.2138</v>
+      </c>
+      <c r="V68">
+        <v>0.07134688081726753</v>
+      </c>
+      <c r="W68">
+        <v>0.1985460368812682</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>0.7134688081726754</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.2079013138783241</v>
+      </c>
+      <c r="C69">
+        <v>-25.69355048779219</v>
+      </c>
+      <c r="D69">
+        <v>46.23444951220781</v>
+      </c>
+      <c r="E69">
+        <v>24.40800000000001</v>
+      </c>
+      <c r="F69">
+        <v>75.30800000000001</v>
+      </c>
+      <c r="G69">
+        <v>3.38</v>
+      </c>
+      <c r="H69">
+        <v>61.5</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>12</v>
+      </c>
+      <c r="K69">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="L69">
+        <v>11.316</v>
+      </c>
+      <c r="M69">
+        <v>16.1008504</v>
+      </c>
+      <c r="N69">
+        <v>-4.784850400000002</v>
+      </c>
+      <c r="O69">
+        <v>-0.47848504</v>
+      </c>
+      <c r="P69">
+        <v>-4.306365360000002</v>
+      </c>
+      <c r="Q69">
+        <v>-3.622365360000002</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.2264331198081428</v>
+      </c>
+      <c r="T69">
+        <v>2.163388782761441</v>
+      </c>
+      <c r="U69">
+        <v>0.2138</v>
+      </c>
+      <c r="V69">
+        <v>0.07028200199909936</v>
+      </c>
+      <c r="W69">
+        <v>0.1987737079725925</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>0.7028200199909937</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.2096513138783241</v>
+      </c>
+      <c r="C70">
+        <v>-27.29112183359987</v>
+      </c>
+      <c r="D70">
+        <v>45.76087816640014</v>
+      </c>
+      <c r="E70">
+        <v>25.53200000000002</v>
+      </c>
+      <c r="F70">
+        <v>76.43200000000002</v>
+      </c>
+      <c r="G70">
+        <v>3.38</v>
+      </c>
+      <c r="H70">
+        <v>61.5</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>12</v>
+      </c>
+      <c r="K70">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="L70">
+        <v>11.316</v>
+      </c>
+      <c r="M70">
+        <v>16.3411616</v>
+      </c>
+      <c r="N70">
+        <v>-5.025161600000002</v>
+      </c>
+      <c r="O70">
+        <v>-0.5025161600000001</v>
+      </c>
+      <c r="P70">
+        <v>-4.522645440000002</v>
+      </c>
+      <c r="Q70">
+        <v>-3.838645440000002</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.2322966548021472</v>
+      </c>
+      <c r="T70">
+        <v>2.230994682222736</v>
+      </c>
+      <c r="U70">
+        <v>0.2138</v>
+      </c>
+      <c r="V70">
+        <v>0.06924844314617142</v>
+      </c>
+      <c r="W70">
+        <v>0.1989946828553485</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>0.6924844314617143</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.2114013138783241</v>
+      </c>
+      <c r="C71">
+        <v>-28.87909012556578</v>
+      </c>
+      <c r="D71">
+        <v>45.29690987443423</v>
+      </c>
+      <c r="E71">
+        <v>26.65600000000001</v>
+      </c>
+      <c r="F71">
+        <v>77.55600000000001</v>
+      </c>
+      <c r="G71">
+        <v>3.38</v>
+      </c>
+      <c r="H71">
+        <v>61.5</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>12</v>
+      </c>
+      <c r="K71">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="L71">
+        <v>11.316</v>
+      </c>
+      <c r="M71">
+        <v>16.5814728</v>
+      </c>
+      <c r="N71">
+        <v>-5.2654728</v>
+      </c>
+      <c r="O71">
+        <v>-0.5265472799999998</v>
+      </c>
+      <c r="P71">
+        <v>-4.73892552</v>
+      </c>
+      <c r="Q71">
+        <v>-4.054925519999999</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.2385384823764101</v>
+      </c>
+      <c r="T71">
+        <v>2.302962252617018</v>
+      </c>
+      <c r="U71">
+        <v>0.2138</v>
+      </c>
+      <c r="V71">
+        <v>0.0682448425208646</v>
+      </c>
+      <c r="W71">
+        <v>0.1992092526690391</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>0.6824484252086462</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.2131513138783241</v>
+      </c>
+      <c r="C72">
+        <v>-30.45774452717001</v>
+      </c>
+      <c r="D72">
+        <v>44.84225547282999</v>
+      </c>
+      <c r="E72">
+        <v>27.78000000000001</v>
+      </c>
+      <c r="F72">
+        <v>78.68000000000001</v>
+      </c>
+      <c r="G72">
+        <v>3.38</v>
+      </c>
+      <c r="H72">
+        <v>61.5</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>12</v>
+      </c>
+      <c r="K72">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="L72">
+        <v>11.316</v>
+      </c>
+      <c r="M72">
+        <v>16.821784</v>
+      </c>
+      <c r="N72">
+        <v>-5.505784</v>
+      </c>
+      <c r="O72">
+        <v>-0.5505783999999999</v>
+      </c>
+      <c r="P72">
+        <v>-4.9552056</v>
+      </c>
+      <c r="Q72">
+        <v>-4.2712056</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.245196431788957</v>
+      </c>
+      <c r="T72">
+        <v>2.379727661037585</v>
+      </c>
+      <c r="U72">
+        <v>0.2138</v>
+      </c>
+      <c r="V72">
+        <v>0.06726991619913797</v>
+      </c>
+      <c r="W72">
+        <v>0.1994176919166243</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>0.6726991619913798</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.2149013138783241</v>
+      </c>
+      <c r="C73">
+        <v>-32.02736270768892</v>
+      </c>
+      <c r="D73">
+        <v>44.39663729231108</v>
+      </c>
+      <c r="E73">
+        <v>28.904</v>
+      </c>
+      <c r="F73">
+        <v>79.804</v>
+      </c>
+      <c r="G73">
+        <v>3.38</v>
+      </c>
+      <c r="H73">
+        <v>61.5</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>12</v>
+      </c>
+      <c r="K73">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="L73">
+        <v>11.316</v>
+      </c>
+      <c r="M73">
+        <v>17.0620952</v>
+      </c>
+      <c r="N73">
+        <v>-5.746095199999997</v>
+      </c>
+      <c r="O73">
+        <v>-0.5746095199999997</v>
+      </c>
+      <c r="P73">
+        <v>-5.171485679999998</v>
+      </c>
+      <c r="Q73">
+        <v>-4.487485679999998</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.2523135501265072</v>
+      </c>
+      <c r="T73">
+        <v>2.461787235556121</v>
+      </c>
+      <c r="U73">
+        <v>0.2138</v>
+      </c>
+      <c r="V73">
+        <v>0.06632245259069941</v>
+      </c>
+      <c r="W73">
+        <v>0.1996202596361085</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>0.6632245259069942</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.2166513138783241</v>
+      </c>
+      <c r="C74">
+        <v>-33.58821140769177</v>
+      </c>
+      <c r="D74">
+        <v>43.95978859230823</v>
+      </c>
+      <c r="E74">
+        <v>30.028</v>
+      </c>
+      <c r="F74">
+        <v>80.928</v>
+      </c>
+      <c r="G74">
+        <v>3.38</v>
+      </c>
+      <c r="H74">
+        <v>61.5</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>12</v>
+      </c>
+      <c r="K74">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="L74">
+        <v>11.316</v>
+      </c>
+      <c r="M74">
+        <v>17.3024064</v>
+      </c>
+      <c r="N74">
+        <v>-5.986406399999998</v>
+      </c>
+      <c r="O74">
+        <v>-0.5986406399999997</v>
+      </c>
+      <c r="P74">
+        <v>-5.387765759999999</v>
+      </c>
+      <c r="Q74">
+        <v>-4.703765759999999</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.2599390340595967</v>
+      </c>
+      <c r="T74">
+        <v>2.549708208254554</v>
+      </c>
+      <c r="U74">
+        <v>0.2138</v>
+      </c>
+      <c r="V74">
+        <v>0.06540130741582857</v>
+      </c>
+      <c r="W74">
+        <v>0.1998172004744958</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>0.6540130741582859</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.2184013138783241</v>
+      </c>
+      <c r="C75">
+        <v>-35.14054697147645</v>
+      </c>
+      <c r="D75">
+        <v>43.53145302852356</v>
+      </c>
+      <c r="E75">
+        <v>31.15200000000001</v>
+      </c>
+      <c r="F75">
+        <v>82.05200000000001</v>
+      </c>
+      <c r="G75">
+        <v>3.38</v>
+      </c>
+      <c r="H75">
+        <v>61.5</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>12</v>
+      </c>
+      <c r="K75">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="L75">
+        <v>11.316</v>
+      </c>
+      <c r="M75">
+        <v>17.5427176</v>
+      </c>
+      <c r="N75">
+        <v>-6.226717599999999</v>
+      </c>
+      <c r="O75">
+        <v>-0.6226717599999998</v>
+      </c>
+      <c r="P75">
+        <v>-5.60404584</v>
+      </c>
+      <c r="Q75">
+        <v>-4.920045839999999</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.2681293686543966</v>
+      </c>
+      <c r="T75">
+        <v>2.644141845597316</v>
+      </c>
+      <c r="U75">
+        <v>0.2138</v>
+      </c>
+      <c r="V75">
+        <v>0.06450539909506381</v>
+      </c>
+      <c r="W75">
+        <v>0.2000087456734753</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>0.6450539909506381</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.2201513138783241</v>
+      </c>
+      <c r="C76">
+        <v>-36.68461584867811</v>
+      </c>
+      <c r="D76">
+        <v>43.11138415132189</v>
+      </c>
+      <c r="E76">
+        <v>32.276</v>
+      </c>
+      <c r="F76">
+        <v>83.176</v>
+      </c>
+      <c r="G76">
+        <v>3.38</v>
+      </c>
+      <c r="H76">
+        <v>61.5</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>12</v>
+      </c>
+      <c r="K76">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="L76">
+        <v>11.316</v>
+      </c>
+      <c r="M76">
+        <v>17.7830288</v>
+      </c>
+      <c r="N76">
+        <v>-6.4670288</v>
+      </c>
+      <c r="O76">
+        <v>-0.6467028799999999</v>
+      </c>
+      <c r="P76">
+        <v>-5.82032592</v>
+      </c>
+      <c r="Q76">
+        <v>-5.13632592</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.276949728987258</v>
+      </c>
+      <c r="T76">
+        <v>2.74583960888952</v>
+      </c>
+      <c r="U76">
+        <v>0.2138</v>
+      </c>
+      <c r="V76">
+        <v>0.06363370451269808</v>
+      </c>
+      <c r="W76">
+        <v>0.2001951139751851</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>0.6363370451269809</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.2219013138783241</v>
+      </c>
+      <c r="C77">
+        <v>-38.22065506711295</v>
+      </c>
+      <c r="D77">
+        <v>42.69934493288706</v>
+      </c>
+      <c r="E77">
+        <v>33.40000000000001</v>
+      </c>
+      <c r="F77">
+        <v>84.30000000000001</v>
+      </c>
+      <c r="G77">
+        <v>3.38</v>
+      </c>
+      <c r="H77">
+        <v>61.5</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>12</v>
+      </c>
+      <c r="K77">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="L77">
+        <v>11.316</v>
+      </c>
+      <c r="M77">
+        <v>18.02334</v>
+      </c>
+      <c r="N77">
+        <v>-6.70734</v>
+      </c>
+      <c r="O77">
+        <v>-0.6707339999999998</v>
+      </c>
+      <c r="P77">
+        <v>-6.036606000000001</v>
+      </c>
+      <c r="Q77">
+        <v>-5.352606000000001</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.2864757181467484</v>
+      </c>
+      <c r="T77">
+        <v>2.855673193245101</v>
+      </c>
+      <c r="U77">
+        <v>0.2138</v>
+      </c>
+      <c r="V77">
+        <v>0.06278525511919543</v>
+      </c>
+      <c r="W77">
+        <v>0.200376512455516</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>0.6278525511919544</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.2236513138783241</v>
+      </c>
+      <c r="C78">
+        <v>-39.74889267876302</v>
+      </c>
+      <c r="D78">
+        <v>42.29510732123698</v>
+      </c>
+      <c r="E78">
+        <v>34.52400000000001</v>
+      </c>
+      <c r="F78">
+        <v>85.42400000000001</v>
+      </c>
+      <c r="G78">
+        <v>3.38</v>
+      </c>
+      <c r="H78">
+        <v>61.5</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>12</v>
+      </c>
+      <c r="K78">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="L78">
+        <v>11.316</v>
+      </c>
+      <c r="M78">
+        <v>18.2636512</v>
+      </c>
+      <c r="N78">
+        <v>-6.947651200000001</v>
+      </c>
+      <c r="O78">
+        <v>-0.6947651199999999</v>
+      </c>
+      <c r="P78">
+        <v>-6.252886080000001</v>
+      </c>
+      <c r="Q78">
+        <v>-5.568886080000001</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.2967955397361963</v>
+      </c>
+      <c r="T78">
+        <v>2.974659576296981</v>
+      </c>
+      <c r="U78">
+        <v>0.2138</v>
+      </c>
+      <c r="V78">
+        <v>0.06195913334131128</v>
+      </c>
+      <c r="W78">
+        <v>0.2005531372916276</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>0.6195913334131129</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.2254013138783241</v>
+      </c>
+      <c r="C79">
+        <v>-41.26954818066602</v>
+      </c>
+      <c r="D79">
+        <v>41.89845181933398</v>
+      </c>
+      <c r="E79">
+        <v>35.648</v>
+      </c>
+      <c r="F79">
+        <v>86.548</v>
+      </c>
+      <c r="G79">
+        <v>3.38</v>
+      </c>
+      <c r="H79">
+        <v>61.5</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>12</v>
+      </c>
+      <c r="K79">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="L79">
+        <v>11.316</v>
+      </c>
+      <c r="M79">
+        <v>18.5039624</v>
+      </c>
+      <c r="N79">
+        <v>-7.187962399999998</v>
+      </c>
+      <c r="O79">
+        <v>-0.7187962399999996</v>
+      </c>
+      <c r="P79">
+        <v>-6.469166159999999</v>
+      </c>
+      <c r="Q79">
+        <v>-5.785166159999998</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.3080127371160309</v>
+      </c>
+      <c r="T79">
+        <v>3.103992601353371</v>
+      </c>
+      <c r="U79">
+        <v>0.2138</v>
+      </c>
+      <c r="V79">
+        <v>0.06115446927194361</v>
+      </c>
+      <c r="W79">
+        <v>0.2007251744696585</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>0.6115446927194362</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.2271513138783241</v>
+      </c>
+      <c r="C80">
+        <v>-42.78283291234142</v>
+      </c>
+      <c r="D80">
+        <v>41.50916708765859</v>
+      </c>
+      <c r="E80">
+        <v>36.77200000000001</v>
+      </c>
+      <c r="F80">
+        <v>87.67200000000001</v>
+      </c>
+      <c r="G80">
+        <v>3.38</v>
+      </c>
+      <c r="H80">
+        <v>61.5</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>12</v>
+      </c>
+      <c r="K80">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="L80">
+        <v>11.316</v>
+      </c>
+      <c r="M80">
+        <v>18.7442736</v>
+      </c>
+      <c r="N80">
+        <v>-7.428273600000002</v>
+      </c>
+      <c r="O80">
+        <v>-0.74282736</v>
+      </c>
+      <c r="P80">
+        <v>-6.685446240000003</v>
+      </c>
+      <c r="Q80">
+        <v>-6.001446240000003</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.3202496797122141</v>
+      </c>
+      <c r="T80">
+        <v>3.245083174142161</v>
+      </c>
+      <c r="U80">
+        <v>0.2138</v>
+      </c>
+      <c r="V80">
+        <v>0.06037043761461098</v>
+      </c>
+      <c r="W80">
+        <v>0.2008928004379961</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>0.6037043761461099</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.2289013138783241</v>
+      </c>
+      <c r="C81">
+        <v>-44.28895043126555</v>
+      </c>
+      <c r="D81">
+        <v>41.12704956873445</v>
+      </c>
+      <c r="E81">
+        <v>37.89600000000001</v>
+      </c>
+      <c r="F81">
+        <v>88.79600000000001</v>
+      </c>
+      <c r="G81">
+        <v>3.38</v>
+      </c>
+      <c r="H81">
+        <v>61.5</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>12</v>
+      </c>
+      <c r="K81">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="L81">
+        <v>11.316</v>
+      </c>
+      <c r="M81">
+        <v>18.9845848</v>
+      </c>
+      <c r="N81">
+        <v>-7.6685848</v>
+      </c>
+      <c r="O81">
+        <v>-0.7668584799999998</v>
+      </c>
+      <c r="P81">
+        <v>-6.90172632</v>
+      </c>
+      <c r="Q81">
+        <v>-6.21772632</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.3336520454127958</v>
+      </c>
+      <c r="T81">
+        <v>3.399610944339407</v>
+      </c>
+      <c r="U81">
+        <v>0.2138</v>
+      </c>
+      <c r="V81">
+        <v>0.05960625485999566</v>
+      </c>
+      <c r="W81">
+        <v>0.2010561827109329</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>0.5960625485999568</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.2306513138783241</v>
+      </c>
+      <c r="C82">
+        <v>-45.78809686779677</v>
+      </c>
+      <c r="D82">
+        <v>40.75190313220324</v>
+      </c>
+      <c r="E82">
+        <v>39.02000000000002</v>
+      </c>
+      <c r="F82">
+        <v>89.92000000000002</v>
+      </c>
+      <c r="G82">
+        <v>3.38</v>
+      </c>
+      <c r="H82">
+        <v>61.5</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>12</v>
+      </c>
+      <c r="K82">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="L82">
+        <v>11.316</v>
+      </c>
+      <c r="M82">
+        <v>19.224896</v>
+      </c>
+      <c r="N82">
+        <v>-7.908896</v>
+      </c>
+      <c r="O82">
+        <v>-0.7908895999999999</v>
+      </c>
+      <c r="P82">
+        <v>-7.118006400000001</v>
+      </c>
+      <c r="Q82">
+        <v>-6.4340064</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.3483946476834355</v>
+      </c>
+      <c r="T82">
+        <v>3.569591491556377</v>
+      </c>
+      <c r="U82">
+        <v>0.2138</v>
+      </c>
+      <c r="V82">
+        <v>0.05886117667424572</v>
+      </c>
+      <c r="W82">
+        <v>0.2012154804270463</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>0.5886117667424573</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.2324013138783241</v>
+      </c>
+      <c r="C83">
+        <v>-47.28046126085135</v>
+      </c>
+      <c r="D83">
+        <v>40.38353873914866</v>
+      </c>
+      <c r="E83">
+        <v>40.14400000000001</v>
+      </c>
+      <c r="F83">
+        <v>91.04400000000001</v>
+      </c>
+      <c r="G83">
+        <v>3.38</v>
+      </c>
+      <c r="H83">
+        <v>61.5</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>12</v>
+      </c>
+      <c r="K83">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="L83">
+        <v>11.316</v>
+      </c>
+      <c r="M83">
+        <v>19.4652072</v>
+      </c>
+      <c r="N83">
+        <v>-8.149207200000001</v>
+      </c>
+      <c r="O83">
+        <v>-0.8149207199999999</v>
+      </c>
+      <c r="P83">
+        <v>-7.334286480000001</v>
+      </c>
+      <c r="Q83">
+        <v>-6.650286480000001</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.364689102824669</v>
+      </c>
+      <c r="T83">
+        <v>3.757464727954082</v>
+      </c>
+      <c r="U83">
+        <v>0.2138</v>
+      </c>
+      <c r="V83">
+        <v>0.0581344954807365</v>
+      </c>
+      <c r="W83">
+        <v>0.2013708448662185</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>0.5813449548073653</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.2341513138783241</v>
+      </c>
+      <c r="C84">
+        <v>-48.7662258755369</v>
+      </c>
+      <c r="D84">
+        <v>40.0217741244631</v>
+      </c>
+      <c r="E84">
+        <v>41.26800000000001</v>
+      </c>
+      <c r="F84">
+        <v>92.16800000000001</v>
+      </c>
+      <c r="G84">
+        <v>3.38</v>
+      </c>
+      <c r="H84">
+        <v>61.5</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>12</v>
+      </c>
+      <c r="K84">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="L84">
+        <v>11.316</v>
+      </c>
+      <c r="M84">
+        <v>19.7055184</v>
+      </c>
+      <c r="N84">
+        <v>-8.389518399999998</v>
+      </c>
+      <c r="O84">
+        <v>-0.8389518399999997</v>
+      </c>
+      <c r="P84">
+        <v>-7.550566559999998</v>
+      </c>
+      <c r="Q84">
+        <v>-6.866566559999998</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.3827940529815951</v>
+      </c>
+      <c r="T84">
+        <v>3.966212768395975</v>
+      </c>
+      <c r="U84">
+        <v>0.2138</v>
+      </c>
+      <c r="V84">
+        <v>0.05742553821877631</v>
+      </c>
+      <c r="W84">
+        <v>0.2015224199288256</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>0.5742553821877633</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.2359013138783241</v>
+      </c>
+      <c r="C85">
+        <v>-50.24556650386498</v>
+      </c>
+      <c r="D85">
+        <v>39.66643349613503</v>
+      </c>
+      <c r="E85">
+        <v>42.39200000000002</v>
+      </c>
+      <c r="F85">
+        <v>93.29200000000002</v>
+      </c>
+      <c r="G85">
+        <v>3.38</v>
+      </c>
+      <c r="H85">
+        <v>61.5</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>12</v>
+      </c>
+      <c r="K85">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="L85">
+        <v>11.316</v>
+      </c>
+      <c r="M85">
+        <v>19.9458296</v>
+      </c>
+      <c r="N85">
+        <v>-8.629829600000003</v>
+      </c>
+      <c r="O85">
+        <v>-0.8629829600000001</v>
+      </c>
+      <c r="P85">
+        <v>-7.766846640000002</v>
+      </c>
+      <c r="Q85">
+        <v>-7.082846640000002</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.4030289972746301</v>
+      </c>
+      <c r="T85">
+        <v>4.199519401831033</v>
+      </c>
+      <c r="U85">
+        <v>0.2138</v>
+      </c>
+      <c r="V85">
+        <v>0.05673366426433322</v>
+      </c>
+      <c r="W85">
+        <v>0.2016703425802855</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>0.5673366426433323</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.2376513138783241</v>
+      </c>
+      <c r="C86">
+        <v>-51.71865274958476</v>
+      </c>
+      <c r="D86">
+        <v>39.31734725041524</v>
+      </c>
+      <c r="E86">
+        <v>43.516</v>
+      </c>
+      <c r="F86">
+        <v>94.416</v>
+      </c>
+      <c r="G86">
+        <v>3.38</v>
+      </c>
+      <c r="H86">
+        <v>61.5</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>12</v>
+      </c>
+      <c r="K86">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="L86">
+        <v>11.316</v>
+      </c>
+      <c r="M86">
+        <v>20.1861408</v>
+      </c>
+      <c r="N86">
+        <v>-8.870140799999996</v>
+      </c>
+      <c r="O86">
+        <v>-0.8870140799999994</v>
+      </c>
+      <c r="P86">
+        <v>-7.983126719999997</v>
+      </c>
+      <c r="Q86">
+        <v>-7.299126719999997</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.4257933096042942</v>
+      </c>
+      <c r="T86">
+        <v>4.461989364445469</v>
+      </c>
+      <c r="U86">
+        <v>0.2138</v>
+      </c>
+      <c r="V86">
+        <v>0.05605826349928165</v>
+      </c>
+      <c r="W86">
+        <v>0.2018147432638536</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>0.5605826349928166</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.2394013138783241</v>
+      </c>
+      <c r="C87">
+        <v>-53.18564829810826</v>
+      </c>
+      <c r="D87">
+        <v>38.97435170189175</v>
+      </c>
+      <c r="E87">
+        <v>44.64000000000001</v>
+      </c>
+      <c r="F87">
+        <v>95.54000000000001</v>
+      </c>
+      <c r="G87">
+        <v>3.38</v>
+      </c>
+      <c r="H87">
+        <v>61.5</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>12</v>
+      </c>
+      <c r="K87">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="L87">
+        <v>11.316</v>
+      </c>
+      <c r="M87">
+        <v>20.426452</v>
+      </c>
+      <c r="N87">
+        <v>-9.110452</v>
+      </c>
+      <c r="O87">
+        <v>-0.9110451999999999</v>
+      </c>
+      <c r="P87">
+        <v>-8.1994068</v>
+      </c>
+      <c r="Q87">
+        <v>-7.5154068</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.4515928635779139</v>
+      </c>
+      <c r="T87">
+        <v>4.759455322075168</v>
+      </c>
+      <c r="U87">
+        <v>0.2138</v>
+      </c>
+      <c r="V87">
+        <v>0.05539875451693714</v>
+      </c>
+      <c r="W87">
+        <v>0.2019557462842788</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>0.5539875451693715</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.2411513138783241</v>
+      </c>
+      <c r="C88">
+        <v>-54.64671117242852</v>
+      </c>
+      <c r="D88">
+        <v>38.63728882757148</v>
+      </c>
+      <c r="E88">
+        <v>45.764</v>
+      </c>
+      <c r="F88">
+        <v>96.664</v>
+      </c>
+      <c r="G88">
+        <v>3.38</v>
+      </c>
+      <c r="H88">
+        <v>61.5</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>12</v>
+      </c>
+      <c r="K88">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="L88">
+        <v>11.316</v>
+      </c>
+      <c r="M88">
+        <v>20.6667632</v>
+      </c>
+      <c r="N88">
+        <v>-9.350763199999998</v>
+      </c>
+      <c r="O88">
+        <v>-0.9350763199999995</v>
+      </c>
+      <c r="P88">
+        <v>-8.415686879999997</v>
+      </c>
+      <c r="Q88">
+        <v>-7.731686879999997</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.4810780681191935</v>
+      </c>
+      <c r="T88">
+        <v>5.099416416509109</v>
+      </c>
+      <c r="U88">
+        <v>0.2138</v>
+      </c>
+      <c r="V88">
+        <v>0.05475458295278672</v>
+      </c>
+      <c r="W88">
+        <v>0.2020934701646942</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>0.5475458295278672</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.2429013138783241</v>
+      </c>
+      <c r="C89">
+        <v>-56.10199397587269</v>
+      </c>
+      <c r="D89">
+        <v>38.30600602412731</v>
+      </c>
+      <c r="E89">
+        <v>46.88800000000001</v>
+      </c>
+      <c r="F89">
+        <v>97.78800000000001</v>
+      </c>
+      <c r="G89">
+        <v>3.38</v>
+      </c>
+      <c r="H89">
+        <v>61.5</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>12</v>
+      </c>
+      <c r="K89">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="L89">
+        <v>11.316</v>
+      </c>
+      <c r="M89">
+        <v>20.9070744</v>
+      </c>
+      <c r="N89">
+        <v>-9.591074400000002</v>
+      </c>
+      <c r="O89">
+        <v>-0.9591074399999999</v>
+      </c>
+      <c r="P89">
+        <v>-8.631966960000002</v>
+      </c>
+      <c r="Q89">
+        <v>-7.947966960000001</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.5150994579745161</v>
+      </c>
+      <c r="T89">
+        <v>5.491679217779041</v>
+      </c>
+      <c r="U89">
+        <v>0.2138</v>
+      </c>
+      <c r="V89">
+        <v>0.05412521993034088</v>
+      </c>
+      <c r="W89">
+        <v>0.2022280279788931</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>0.541252199303409</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.2446513138783241</v>
+      </c>
+      <c r="C90">
+        <v>-57.55164412247242</v>
+      </c>
+      <c r="D90">
+        <v>37.98035587752759</v>
+      </c>
+      <c r="E90">
+        <v>48.01200000000001</v>
+      </c>
+      <c r="F90">
+        <v>98.91200000000001</v>
+      </c>
+      <c r="G90">
+        <v>3.38</v>
+      </c>
+      <c r="H90">
+        <v>61.5</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>12</v>
+      </c>
+      <c r="K90">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="L90">
+        <v>11.316</v>
+      </c>
+      <c r="M90">
+        <v>21.1473856</v>
+      </c>
+      <c r="N90">
+        <v>-9.831385599999999</v>
+      </c>
+      <c r="O90">
+        <v>-0.9831385599999997</v>
+      </c>
+      <c r="P90">
+        <v>-8.848247039999999</v>
+      </c>
+      <c r="Q90">
+        <v>-8.164247039999999</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.5547910794723925</v>
+      </c>
+      <c r="T90">
+        <v>5.949319152593961</v>
+      </c>
+      <c r="U90">
+        <v>0.2138</v>
+      </c>
+      <c r="V90">
+        <v>0.05351016061295065</v>
+      </c>
+      <c r="W90">
+        <v>0.2023595276609511</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>0.5351016061295066</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.2464013138783241</v>
+      </c>
+      <c r="C91">
+        <v>-58.9958040556828</v>
+      </c>
+      <c r="D91">
+        <v>37.66019594431719</v>
+      </c>
+      <c r="E91">
+        <v>49.136</v>
+      </c>
+      <c r="F91">
+        <v>100.036</v>
+      </c>
+      <c r="G91">
+        <v>3.38</v>
+      </c>
+      <c r="H91">
+        <v>61.5</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>12</v>
+      </c>
+      <c r="K91">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="L91">
+        <v>11.316</v>
+      </c>
+      <c r="M91">
+        <v>21.3876968</v>
+      </c>
+      <c r="N91">
+        <v>-10.0716968</v>
+      </c>
+      <c r="O91">
+        <v>-1.00716968</v>
+      </c>
+      <c r="P91">
+        <v>-9.064527119999999</v>
+      </c>
+      <c r="Q91">
+        <v>-8.38052712</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.6016993594244282</v>
+      </c>
+      <c r="T91">
+        <v>6.490166348284322</v>
+      </c>
+      <c r="U91">
+        <v>0.2138</v>
+      </c>
+      <c r="V91">
+        <v>0.05290892285325458</v>
+      </c>
+      <c r="W91">
+        <v>0.2024880722939742</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>0.5290892285325459</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.2481513138783241</v>
+      </c>
+      <c r="C92">
+        <v>-60.43461145613153</v>
+      </c>
+      <c r="D92">
+        <v>37.34538854386848</v>
+      </c>
+      <c r="E92">
+        <v>50.26000000000001</v>
+      </c>
+      <c r="F92">
+        <v>101.16</v>
+      </c>
+      <c r="G92">
+        <v>3.38</v>
+      </c>
+      <c r="H92">
+        <v>61.5</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>12</v>
+      </c>
+      <c r="K92">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="L92">
+        <v>11.316</v>
+      </c>
+      <c r="M92">
+        <v>21.628008</v>
+      </c>
+      <c r="N92">
+        <v>-10.312008</v>
+      </c>
+      <c r="O92">
+        <v>-1.0312008</v>
+      </c>
+      <c r="P92">
+        <v>-9.2808072</v>
+      </c>
+      <c r="Q92">
+        <v>-8.596807200000001</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.6579892953668711</v>
+      </c>
+      <c r="T92">
+        <v>7.139182983112755</v>
+      </c>
+      <c r="U92">
+        <v>0.2138</v>
+      </c>
+      <c r="V92">
+        <v>0.05232104593266286</v>
+      </c>
+      <c r="W92">
+        <v>0.2026137603795967</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>0.5232104593266287</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.2499013138783241</v>
+      </c>
+      <c r="C93">
+        <v>-61.86819943903454</v>
+      </c>
+      <c r="D93">
+        <v>37.03580056096546</v>
+      </c>
+      <c r="E93">
+        <v>51.38400000000001</v>
+      </c>
+      <c r="F93">
+        <v>102.284</v>
+      </c>
+      <c r="G93">
+        <v>3.38</v>
+      </c>
+      <c r="H93">
+        <v>61.5</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>12</v>
+      </c>
+      <c r="K93">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="L93">
+        <v>11.316</v>
+      </c>
+      <c r="M93">
+        <v>21.8683192</v>
+      </c>
+      <c r="N93">
+        <v>-10.5523192</v>
+      </c>
+      <c r="O93">
+        <v>-1.05523192</v>
+      </c>
+      <c r="P93">
+        <v>-9.497087280000001</v>
+      </c>
+      <c r="Q93">
+        <v>-8.813087280000001</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>0.7267881059631902</v>
+      </c>
+      <c r="T93">
+        <v>7.93242553679195</v>
+      </c>
+      <c r="U93">
+        <v>0.2138</v>
+      </c>
+      <c r="V93">
+        <v>0.05174608938395227</v>
+      </c>
+      <c r="W93">
+        <v>0.202736686089711</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>0.5174608938395229</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.2516513138783241</v>
+      </c>
+      <c r="C94">
+        <v>-63.29669674187356</v>
+      </c>
+      <c r="D94">
+        <v>36.73130325812645</v>
+      </c>
+      <c r="E94">
+        <v>52.50800000000002</v>
+      </c>
+      <c r="F94">
+        <v>103.408</v>
+      </c>
+      <c r="G94">
+        <v>3.38</v>
+      </c>
+      <c r="H94">
+        <v>61.5</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>12</v>
+      </c>
+      <c r="K94">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="L94">
+        <v>11.316</v>
+      </c>
+      <c r="M94">
+        <v>22.1086304</v>
+      </c>
+      <c r="N94">
+        <v>-10.7926304</v>
+      </c>
+      <c r="O94">
+        <v>-1.07926304</v>
+      </c>
+      <c r="P94">
+        <v>-9.713367360000001</v>
+      </c>
+      <c r="Q94">
+        <v>-9.029367360000002</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>0.8127866192085891</v>
+      </c>
+      <c r="T94">
+        <v>8.923978728890946</v>
+      </c>
+      <c r="U94">
+        <v>0.2138</v>
+      </c>
+      <c r="V94">
+        <v>0.05118363189064844</v>
+      </c>
+      <c r="W94">
+        <v>0.2028569395017794</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>0.5118363189064845</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.2534013138783241</v>
+      </c>
+      <c r="C95">
+        <v>-64.72022790289043</v>
+      </c>
+      <c r="D95">
+        <v>36.43177209710958</v>
+      </c>
+      <c r="E95">
+        <v>53.63200000000001</v>
+      </c>
+      <c r="F95">
+        <v>104.532</v>
+      </c>
+      <c r="G95">
+        <v>3.38</v>
+      </c>
+      <c r="H95">
+        <v>61.5</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>12</v>
+      </c>
+      <c r="K95">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="L95">
+        <v>11.316</v>
+      </c>
+      <c r="M95">
+        <v>22.3489416</v>
+      </c>
+      <c r="N95">
+        <v>-11.0329416</v>
+      </c>
+      <c r="O95">
+        <v>-1.10329416</v>
+      </c>
+      <c r="P95">
+        <v>-9.92964744</v>
+      </c>
+      <c r="Q95">
+        <v>-9.245647440000001</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>0.9233561362383877</v>
+      </c>
+      <c r="T95">
+        <v>10.19883283301823</v>
+      </c>
+      <c r="U95">
+        <v>0.2138</v>
+      </c>
+      <c r="V95">
+        <v>0.05063327025741567</v>
+      </c>
+      <c r="W95">
+        <v>0.2029746068189645</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>0.5063327025741569</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.2551513138783241</v>
+      </c>
+      <c r="C96">
+        <v>-66.13891343091915</v>
+      </c>
+      <c r="D96">
+        <v>36.13708656908086</v>
+      </c>
+      <c r="E96">
+        <v>54.75600000000001</v>
+      </c>
+      <c r="F96">
+        <v>105.656</v>
+      </c>
+      <c r="G96">
+        <v>3.38</v>
+      </c>
+      <c r="H96">
+        <v>61.5</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>12</v>
+      </c>
+      <c r="K96">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="L96">
+        <v>11.316</v>
+      </c>
+      <c r="M96">
+        <v>22.5892528</v>
+      </c>
+      <c r="N96">
+        <v>-11.2732528</v>
+      </c>
+      <c r="O96">
+        <v>-1.12732528</v>
+      </c>
+      <c r="P96">
+        <v>-10.14592752</v>
+      </c>
+      <c r="Q96">
+        <v>-9.461927520000001</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>1.070782158944786</v>
+      </c>
+      <c r="T96">
+        <v>11.89863830518793</v>
+      </c>
+      <c r="U96">
+        <v>0.2138</v>
+      </c>
+      <c r="V96">
+        <v>0.05009461844616657</v>
+      </c>
+      <c r="W96">
+        <v>0.2030897705762096</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>0.5009461844616658</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.2809716424560628</v>
+      </c>
+      <c r="C97">
+        <v>-71.11584781907794</v>
+      </c>
+      <c r="D97">
+        <v>32.28415218092207</v>
+      </c>
+      <c r="E97">
+        <v>55.88000000000002</v>
+      </c>
+      <c r="F97">
+        <v>106.78</v>
+      </c>
+      <c r="G97">
+        <v>3.38</v>
+      </c>
+      <c r="H97">
+        <v>61.5</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>12</v>
+      </c>
+      <c r="K97">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="L97">
+        <v>11.316</v>
+      </c>
+      <c r="M97">
+        <v>25.499064</v>
+      </c>
+      <c r="N97">
+        <v>-14.183064</v>
+      </c>
+      <c r="O97">
+        <v>-1.4183064</v>
+      </c>
+      <c r="P97">
+        <v>-12.7647576</v>
+      </c>
+      <c r="Q97">
+        <v>-12.0807576</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>1.283585162288518</v>
+      </c>
+      <c r="T97">
+        <v>14.35223301619906</v>
+      </c>
+      <c r="U97">
+        <v>0.2388</v>
+      </c>
+      <c r="V97">
+        <v>0.04437809952553551</v>
+      </c>
+      <c r="W97">
+        <v>0.2282025098333021</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>0.4437809952553552</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.2829716424560629</v>
+      </c>
+      <c r="C98">
+        <v>-72.50428599753457</v>
+      </c>
+      <c r="D98">
+        <v>32.01971400246543</v>
+      </c>
+      <c r="E98">
+        <v>57.004</v>
+      </c>
+      <c r="F98">
+        <v>107.904</v>
+      </c>
+      <c r="G98">
+        <v>3.38</v>
+      </c>
+      <c r="H98">
+        <v>61.5</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>12</v>
+      </c>
+      <c r="K98">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="L98">
+        <v>11.316</v>
+      </c>
+      <c r="M98">
+        <v>25.7674752</v>
+      </c>
+      <c r="N98">
+        <v>-14.4514752</v>
+      </c>
+      <c r="O98">
+        <v>-1.44514752</v>
+      </c>
+      <c r="P98">
+        <v>-13.00632768</v>
+      </c>
+      <c r="Q98">
+        <v>-12.32232768</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>1.594781452860644</v>
+      </c>
+      <c r="T98">
+        <v>17.94029127024878</v>
+      </c>
+      <c r="U98">
+        <v>0.2388</v>
+      </c>
+      <c r="V98">
+        <v>0.04391582765547786</v>
+      </c>
+      <c r="W98">
+        <v>0.2283129003558719</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>0.4391582765547787</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.2849716424560628</v>
+      </c>
+      <c r="C99">
+        <v>-73.88842736623977</v>
+      </c>
+      <c r="D99">
+        <v>31.75957263376024</v>
+      </c>
+      <c r="E99">
+        <v>58.12800000000001</v>
+      </c>
+      <c r="F99">
+        <v>109.028</v>
+      </c>
+      <c r="G99">
+        <v>3.38</v>
+      </c>
+      <c r="H99">
+        <v>61.5</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>12</v>
+      </c>
+      <c r="K99">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="L99">
+        <v>11.316</v>
+      </c>
+      <c r="M99">
+        <v>26.0358864</v>
+      </c>
+      <c r="N99">
+        <v>-14.7198864</v>
+      </c>
+      <c r="O99">
+        <v>-1.47198864</v>
+      </c>
+      <c r="P99">
+        <v>-13.24789776</v>
+      </c>
+      <c r="Q99">
+        <v>-12.56389776</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>2.113441937147526</v>
+      </c>
+      <c r="T99">
+        <v>23.92038836033171</v>
+      </c>
+      <c r="U99">
+        <v>0.2388</v>
+      </c>
+      <c r="V99">
+        <v>0.04346308716418427</v>
+      </c>
+      <c r="W99">
+        <v>0.2284210147851928</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>0.4346308716418428</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.2869716424560629</v>
+      </c>
+      <c r="C100">
+        <v>-75.26837580836997</v>
+      </c>
+      <c r="D100">
+        <v>31.50362419163003</v>
+      </c>
+      <c r="E100">
+        <v>59.252</v>
+      </c>
+      <c r="F100">
+        <v>110.152</v>
+      </c>
+      <c r="G100">
+        <v>3.38</v>
+      </c>
+      <c r="H100">
+        <v>61.5</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>12</v>
+      </c>
+      <c r="K100">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="L100">
+        <v>11.316</v>
+      </c>
+      <c r="M100">
+        <v>26.3042976</v>
+      </c>
+      <c r="N100">
+        <v>-14.9882976</v>
+      </c>
+      <c r="O100">
+        <v>-1.49882976</v>
+      </c>
+      <c r="P100">
+        <v>-13.48946784</v>
+      </c>
+      <c r="Q100">
+        <v>-12.80546784</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>3.150762905721288</v>
+      </c>
+      <c r="T100">
+        <v>35.88058254049756</v>
+      </c>
+      <c r="U100">
+        <v>0.2388</v>
+      </c>
+      <c r="V100">
+        <v>0.04301958627475382</v>
+      </c>
+      <c r="W100">
+        <v>0.2285269227975888</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>0.4301958627475383</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.2889716424560629</v>
+      </c>
+      <c r="C101">
+        <v>-76.64423188512066</v>
+      </c>
+      <c r="D101">
+        <v>31.25176811487934</v>
+      </c>
+      <c r="E101">
+        <v>60.37600000000001</v>
+      </c>
+      <c r="F101">
+        <v>111.276</v>
+      </c>
+      <c r="G101">
+        <v>3.38</v>
+      </c>
+      <c r="H101">
+        <v>61.5</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>12</v>
+      </c>
+      <c r="K101">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="L101">
+        <v>11.316</v>
+      </c>
+      <c r="M101">
+        <v>26.5727088</v>
+      </c>
+      <c r="N101">
+        <v>-15.2567088</v>
+      </c>
+      <c r="O101">
+        <v>-1.52567088</v>
+      </c>
+      <c r="P101">
+        <v>-13.73103792</v>
+      </c>
+      <c r="Q101">
+        <v>-13.04703792</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>6.262725811442577</v>
+      </c>
+      <c r="T101">
+        <v>71.76116508099513</v>
+      </c>
+      <c r="U101">
+        <v>0.2388</v>
+      </c>
+      <c r="V101">
+        <v>0.04258504499925125</v>
+      </c>
+      <c r="W101">
+        <v>0.2286306912541788</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>0.4258504499925125</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
